--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3919-2023</t>
+          <t>A 31459-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44952</v>
+        <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -754,25 +754,20 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -787,18 +782,145 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
       </c>
       <c r="T3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Sårläka
+Tallticka
+Talltita
+Ullticka
+Älg
+Björksplintborre
+Mörk husmossa
+Thomsons trägnagare
+Tibast
+Blåsippa
+Spillkråka
+Sångsvan
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 3919-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
         <v>62</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>61</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Stare
@@ -816,158 +938,36 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 31459-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U4" t="n">
-        <v>9</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Sårläka
-Tallticka
-Talltita
-Ullticka
-Älg
-Björksplintborre
-Mörk husmossa
-Thomsons trägnagare
-Tibast
-Blåsippa
-Spillkråka
-Sångsvan
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,11 +1593,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1606,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1618,21 +1623,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1640,153 +1757,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12620-2022</t>
+          <t>A 62578-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44638</v>
+        <v>46007</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,19 +1935,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1959,493 +1959,493 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 12620-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Taggfingersvamp
 Fällmossa
 Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="D16" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 54703-2024</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45618</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>7.7</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,8 +2809,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2819,10 +2824,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2837,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2846,158 +2851,153 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44915</v>
+        <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3063,46 +3063,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,20 +3132,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3168,39 +3168,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44523</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44851</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4895,13 +4895,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4944,7 +4939,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4958,10 +4953,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4973,13 +4968,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5022,7 +5012,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5036,10 +5026,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45447</v>
+        <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5051,13 +5041,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5100,7 +5085,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5114,10 +5099,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44673</v>
+        <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5129,8 +5114,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5173,7 +5163,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5183,14 +5173,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44917</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5203,7 +5193,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5246,7 +5236,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5260,10 +5250,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45756</v>
+        <v>45811</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5275,13 +5265,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5324,7 +5309,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5338,10 +5323,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45842</v>
+        <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5353,13 +5338,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5402,7 +5382,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5416,10 +5396,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44952</v>
+        <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5433,11 +5413,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5497,7 +5477,7 @@
         <v>45861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5558,7 +5538,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5572,10 +5552,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46087</v>
+        <v>45756</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,7 +5573,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5636,7 +5616,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5646,14 +5626,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44924</v>
+        <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5665,13 +5645,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5714,7 +5689,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5724,14 +5699,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45953</v>
+        <v>46087</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5743,8 +5718,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5787,7 +5767,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5801,10 +5781,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44565</v>
+        <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5816,13 +5796,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5865,7 +5840,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5875,14 +5850,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45783</v>
+        <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5895,7 +5870,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5938,7 +5913,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5948,14 +5923,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45518</v>
+        <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5968,7 +5943,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6011,7 +5986,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6021,14 +5996,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45387</v>
+        <v>45953</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6041,7 +6016,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>13.7</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6084,7 +6059,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6098,10 +6073,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44915</v>
+        <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6113,8 +6088,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6157,7 +6137,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6171,10 +6151,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45995</v>
+        <v>45476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6186,8 +6166,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6230,7 +6215,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6244,10 +6229,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45043</v>
+        <v>45848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6260,7 +6245,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6303,7 +6288,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6317,10 +6302,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44920</v>
+        <v>45995</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6333,7 +6318,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6376,7 +6361,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6390,10 +6375,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46049</v>
+        <v>45783</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6406,7 +6391,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6449,7 +6434,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6463,10 +6448,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45848</v>
+        <v>45397</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6479,7 +6464,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>13.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6522,7 +6507,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6536,10 +6521,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44966</v>
+        <v>45043</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6552,7 +6537,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6612,7 +6597,7 @@
         <v>45450</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,7 +6658,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6687,10 +6672,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44678</v>
+        <v>45166</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6703,7 +6688,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6746,7 +6731,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6760,10 +6745,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45113</v>
+        <v>44678</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6776,7 +6761,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6819,7 +6804,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6833,10 +6818,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45629</v>
+        <v>44673</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6849,7 +6834,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6892,7 +6877,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6906,10 +6891,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45629</v>
+        <v>44565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6921,8 +6906,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6982,7 +6972,7 @@
         <v>45842</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7043,7 +7033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7053,14 +7043,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44583</v>
+        <v>46161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7072,13 +7062,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7121,7 +7106,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7131,14 +7116,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45628</v>
+        <v>45716</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7151,7 +7136,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7194,7 +7179,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7208,10 +7193,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46161</v>
+        <v>46182</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7224,7 +7209,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7267,7 +7252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7277,14 +7262,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44673</v>
+        <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7297,7 +7282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>13.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7340,7 +7325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7354,10 +7339,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45716</v>
+        <v>46210</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7370,7 +7355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7413,7 +7398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7427,10 +7412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44905</v>
+        <v>46216</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7442,13 +7427,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7491,7 +7471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7505,10 +7485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45719</v>
+        <v>46216</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7521,7 +7501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7564,7 +7544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7574,14 +7554,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46182</v>
+        <v>46216</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7594,7 +7574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7637,7 +7617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7651,10 +7631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44673</v>
+        <v>46216</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7667,7 +7647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7710,7 +7690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7724,10 +7704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45397</v>
+        <v>44966</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7740,7 +7720,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>13.6</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7783,7 +7763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,14 +7773,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44915</v>
+        <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7813,7 +7793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7856,7 +7836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7870,10 +7850,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44951</v>
+        <v>45300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,13 +7865,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>4.7</v>
+        <v>10.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7934,7 +7909,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7948,10 +7923,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44951</v>
+        <v>45113</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7963,13 +7938,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8012,7 +7982,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8026,10 +7996,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46203</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8042,7 +8012,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>13.8</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8102,7 +8072,7 @@
         <v>45082</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8158,7 +8128,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8172,10 +8142,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44677</v>
+        <v>45476</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8187,8 +8157,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8231,7 +8206,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8245,10 +8220,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46210</v>
+        <v>45629</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8261,7 +8236,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8304,7 +8279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8318,10 +8293,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46216</v>
+        <v>45692</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8334,7 +8309,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8377,7 +8352,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8391,10 +8366,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46216</v>
+        <v>44951</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8406,8 +8381,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8450,7 +8430,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8460,14 +8440,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46216</v>
+        <v>44924</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8479,8 +8459,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8523,7 +8508,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8537,10 +8522,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44937</v>
+        <v>44583</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8552,8 +8537,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8596,7 +8586,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8610,10 +8600,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44937</v>
+        <v>45387</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8626,7 +8616,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8669,7 +8659,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8683,10 +8673,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46216</v>
+        <v>45629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8699,7 +8689,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8742,7 +8732,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8756,10 +8746,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45692</v>
+        <v>44905</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8771,8 +8761,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>11.2</v>
+        <v>4.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8815,7 +8810,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8825,14 +8820,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44935</v>
+        <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8845,7 +8840,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8888,7 +8883,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8898,14 +8893,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45166</v>
+        <v>44673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8918,7 +8913,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8961,7 +8956,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8975,10 +8970,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>44677</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8991,7 +8986,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>10.1</v>
+        <v>5.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9034,7 +9029,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9048,10 +9043,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45155</v>
+        <v>44952</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9063,8 +9058,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45811</v>
+        <v>44920</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31459-2025</t>
+          <t>A 3919-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45833</v>
+        <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -754,20 +754,25 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -782,18 +787,140 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
       </c>
       <c r="T3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U3" t="n">
+        <v>61</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Stare
+Brunlångöra
+Grönsångare
+Nordfladdermus
+Tallticka
+Tofsmes
+Dvärgpipistrell
+Grönsiska
+Kråka
+Kungsfågel
+Större brunfladdermus
+Svartvit flugsnappare
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 31459-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
         <v>17</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>9</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Sårläka
@@ -811,163 +938,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 3919-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>62</v>
-      </c>
-      <c r="U4" t="n">
-        <v>61</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Stare
-Brunlångöra
-Grönsångare
-Nordfladdermus
-Tallticka
-Tofsmes
-Dvärgpipistrell
-Grönsiska
-Kråka
-Kungsfågel
-Större brunfladdermus
-Svartvit flugsnappare
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 3914-2023</t>
+          <t>A 31523-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44952</v>
+        <v>44775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,16 +1593,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1611,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1623,21 +1618,138 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1645,148 +1757,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62578-2025</t>
+          <t>A 54703-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46007</v>
+        <v>45618</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1968,484 +1968,484 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Mindre märgborre
 Vedticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 12620-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 27948-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45817</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>5.6</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 12620-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 31575-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45499</v>
+        <v>44775</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,13 +2809,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2824,10 +2819,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2842,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2851,153 +2846,158 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 30949-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45834</v>
+        <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,20 +3027,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3063,46 +3063,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44915</v>
+        <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3168,46 +3168,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3224,7 +3224,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,17 +3237,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3277,42 +3277,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46008</v>
+        <v>44523</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,11 +3341,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3378,46 +3383,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3431,10 +3440,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44523</v>
+        <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3446,13 +3455,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3461,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3476,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3488,43 +3492,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44747</v>
+        <v>44905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4749,8 +4749,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4793,7 +4798,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4807,10 +4812,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4823,7 +4828,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4866,7 +4871,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4880,10 +4885,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>45719</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4896,7 +4901,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4939,7 +4944,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4953,10 +4958,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>44851</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4969,7 +4974,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5012,7 +5017,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5026,10 +5031,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45155</v>
+        <v>44673</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5042,7 +5047,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5085,7 +5090,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5099,10 +5104,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44951</v>
+        <v>45397</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5114,13 +5119,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>13.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5173,14 +5173,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45518</v>
+        <v>45476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5192,8 +5192,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5236,7 +5241,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5250,10 +5255,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45811</v>
+        <v>46087</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5265,8 +5270,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5309,7 +5319,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5323,10 +5333,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46049</v>
+        <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5338,8 +5348,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5382,7 +5397,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5396,10 +5411,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45842</v>
+        <v>45447</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5432,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5460,7 +5475,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5474,10 +5489,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45861</v>
+        <v>44673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5489,13 +5504,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5538,7 +5548,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5552,10 +5562,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45756</v>
+        <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5567,13 +5577,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5616,7 +5621,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5633,7 +5638,7 @@
         <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5646,7 +5651,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5689,7 +5694,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5703,10 +5708,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46087</v>
+        <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5724,7 +5729,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5767,7 +5772,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5781,10 +5786,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44673</v>
+        <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5797,7 +5802,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5840,7 +5845,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5854,10 +5859,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44935</v>
+        <v>45953</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5870,7 +5875,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5913,7 +5918,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5927,10 +5932,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44917</v>
+        <v>44952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5942,8 +5947,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5986,7 +5996,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5996,14 +6006,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45953</v>
+        <v>45995</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6016,7 +6026,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6059,7 +6069,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6073,10 +6083,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45447</v>
+        <v>45043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6088,13 +6098,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6137,7 +6142,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6151,10 +6156,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45476</v>
+        <v>45848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6166,13 +6171,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6215,7 +6215,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6229,10 +6229,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45848</v>
+        <v>44951</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6244,8 +6244,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6288,7 +6293,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6302,10 +6307,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45995</v>
+        <v>44951</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6317,8 +6322,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6361,7 +6371,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6375,10 +6385,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45783</v>
+        <v>45450</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6390,8 +6400,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6434,7 +6449,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6448,10 +6463,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45397</v>
+        <v>44678</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6464,7 +6479,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>13.6</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6507,7 +6522,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6517,14 +6532,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45043</v>
+        <v>44924</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6536,8 +6551,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6580,7 +6600,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6594,10 +6614,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45450</v>
+        <v>45842</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6658,7 +6678,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6672,10 +6692,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45166</v>
+        <v>45082</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6688,7 +6708,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6731,7 +6751,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6741,14 +6761,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44678</v>
+        <v>46161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6761,7 +6781,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6804,7 +6824,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6818,10 +6838,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44673</v>
+        <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6833,8 +6853,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6877,7 +6902,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6891,10 +6916,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44565</v>
+        <v>45716</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6906,13 +6931,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6955,7 +6975,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6969,10 +6989,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45842</v>
+        <v>46049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6984,13 +7004,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7033,7 +7048,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7043,14 +7058,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46161</v>
+        <v>44677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7063,7 +7078,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7106,7 +7121,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7116,14 +7131,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45716</v>
+        <v>45518</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7136,7 +7151,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7196,7 +7211,7 @@
         <v>46182</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7252,7 +7267,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7266,10 +7281,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46203</v>
+        <v>45387</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7282,7 +7297,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7325,7 +7340,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7339,10 +7354,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46210</v>
+        <v>44915</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7355,7 +7370,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7398,7 +7413,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7412,10 +7427,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46216</v>
+        <v>44920</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7443,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7471,7 +7486,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7485,10 +7500,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46216</v>
+        <v>44937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7501,7 +7516,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7544,7 +7559,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7558,10 +7573,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46216</v>
+        <v>44937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7589,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7617,7 +7632,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7631,10 +7646,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46216</v>
+        <v>44966</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7662,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7690,7 +7705,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7704,10 +7719,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44966</v>
+        <v>46203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7720,7 +7735,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>13.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7763,7 +7778,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7773,14 +7788,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45628</v>
+        <v>45113</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7793,7 +7808,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7836,7 +7851,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7850,10 +7865,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45300</v>
+        <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7866,7 +7881,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>10.1</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7909,7 +7924,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7923,10 +7938,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45113</v>
+        <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7939,7 +7954,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7982,7 +7997,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7996,10 +8011,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45719</v>
+        <v>44583</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8011,8 +8026,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8055,7 +8075,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8069,10 +8089,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45082</v>
+        <v>46210</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8085,7 +8105,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8128,7 +8148,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8138,14 +8158,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45476</v>
+        <v>45628</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8157,13 +8177,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8206,7 +8221,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8220,10 +8235,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45629</v>
+        <v>46216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8236,7 +8251,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8279,7 +8294,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8293,10 +8308,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45692</v>
+        <v>46216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8309,7 +8324,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11.2</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8352,7 +8367,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8366,10 +8381,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44951</v>
+        <v>46216</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8381,13 +8396,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8430,7 +8440,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8440,14 +8450,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44924</v>
+        <v>46216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8459,13 +8469,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8508,7 +8513,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8518,14 +8523,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44583</v>
+        <v>44673</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8537,13 +8542,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45387</v>
+        <v>45692</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>13.7</v>
+        <v>11.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45629</v>
+        <v>44935</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44905</v>
+        <v>45166</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8761,13 +8761,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8810,7 +8805,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8824,10 +8819,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44851</v>
+        <v>45300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8840,7 +8835,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8883,7 +8878,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8893,14 +8888,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44673</v>
+        <v>45155</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8913,7 +8908,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8956,7 +8951,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8970,10 +8965,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44677</v>
+        <v>45811</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8986,7 +8981,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9029,7 +9024,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9043,10 +9038,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44952</v>
+        <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9060,11 +9055,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9107,7 +9102,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9121,10 +9116,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44920</v>
+        <v>45861</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9136,8 +9131,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,11 +1593,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1606,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1618,21 +1623,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1640,153 +1757,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 27948-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45618</v>
+        <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1959,493 +1959,493 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
         <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 12620-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 12620-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,8 +2809,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2819,10 +2824,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2837,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2846,158 +2851,153 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44915</v>
+        <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3063,46 +3063,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46008</v>
+        <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,20 +3132,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3168,46 +3168,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3224,7 +3224,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,16 +3237,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3277,42 +3277,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44523</v>
+        <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,16 +3341,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3383,50 +3378,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3440,10 +3431,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45834</v>
+        <v>44523</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3455,8 +3446,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3465,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3480,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3492,39 +3488,43 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44905</v>
+        <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4749,13 +4749,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4798,7 +4793,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4812,10 +4807,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44747</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4871,7 +4866,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4885,10 +4880,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45719</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4901,7 +4896,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4944,7 +4939,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4958,10 +4953,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44851</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4974,7 +4969,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5017,7 +5012,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5031,10 +5026,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44673</v>
+        <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5047,7 +5042,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5090,7 +5085,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5104,10 +5099,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45397</v>
+        <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5119,8 +5114,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>13.6</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5173,14 +5173,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45476</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5192,13 +5192,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5241,7 +5236,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46087</v>
+        <v>45811</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5270,13 +5265,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5319,7 +5309,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5333,10 +5323,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45476</v>
+        <v>45756</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5354,7 +5344,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5397,7 +5387,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5411,10 +5401,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45447</v>
+        <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5432,7 +5422,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5475,7 +5465,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5489,10 +5479,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44673</v>
+        <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5505,7 +5495,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5548,7 +5538,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5562,10 +5552,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44917</v>
+        <v>45861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5577,8 +5567,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5621,7 +5616,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5635,10 +5630,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44915</v>
+        <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5651,7 +5646,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5694,7 +5689,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5704,14 +5699,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45756</v>
+        <v>44935</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5723,13 +5718,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5772,7 +5762,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5786,10 +5776,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45783</v>
+        <v>44917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5802,7 +5792,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5845,7 +5835,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5855,14 +5845,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45953</v>
+        <v>46049</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5875,7 +5865,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5918,7 +5908,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5928,14 +5918,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44952</v>
+        <v>45953</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5947,13 +5937,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5996,7 +5981,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6010,10 +5995,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45995</v>
+        <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6023,6 +6008,11 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6069,7 +6059,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6083,10 +6073,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45043</v>
+        <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6098,8 +6088,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6142,7 +6137,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6156,10 +6151,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45848</v>
+        <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6172,7 +6167,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>13.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6215,7 +6210,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44951</v>
+        <v>46087</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6246,11 +6241,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6293,7 +6288,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6307,10 +6302,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44951</v>
+        <v>45166</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6322,13 +6317,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6371,7 +6361,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6385,10 +6375,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45450</v>
+        <v>44673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6400,13 +6390,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6449,7 +6434,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6463,10 +6448,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44678</v>
+        <v>44565</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6478,8 +6463,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6522,7 +6512,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6532,14 +6522,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44924</v>
+        <v>45848</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6549,11 +6539,6 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6600,7 +6585,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6614,10 +6599,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6629,13 +6614,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6678,7 +6658,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6692,10 +6672,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45082</v>
+        <v>45783</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6708,7 +6688,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6751,7 +6731,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6761,14 +6741,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46161</v>
+        <v>44966</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6781,7 +6761,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6824,7 +6804,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6838,10 +6818,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44565</v>
+        <v>45043</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6853,13 +6833,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6902,7 +6877,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6912,14 +6887,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45716</v>
+        <v>45628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6932,7 +6907,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6975,7 +6950,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6989,10 +6964,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46049</v>
+        <v>45450</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7004,8 +6979,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7048,7 +7028,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7062,10 +7042,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7078,7 +7058,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7121,7 +7101,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7131,14 +7111,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45518</v>
+        <v>45300</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7151,7 +7131,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>10.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7194,7 +7174,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7204,14 +7184,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46182</v>
+        <v>45842</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7223,8 +7203,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7267,7 +7252,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7281,10 +7266,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45387</v>
+        <v>45113</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7297,7 +7282,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.7</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7340,7 +7325,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7350,14 +7335,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44915</v>
+        <v>46161</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7370,7 +7355,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7413,7 +7398,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7427,10 +7412,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44920</v>
+        <v>45716</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7443,7 +7428,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7486,7 +7471,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7500,10 +7485,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44937</v>
+        <v>45719</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7516,7 +7501,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7559,7 +7544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7569,14 +7554,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44937</v>
+        <v>46182</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7589,7 +7574,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7632,7 +7617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7646,10 +7631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44966</v>
+        <v>45082</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7662,7 +7647,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7705,7 +7690,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7719,10 +7704,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46203</v>
+        <v>45476</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7734,8 +7719,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>13.8</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7778,7 +7768,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7792,10 +7782,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45113</v>
+        <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7808,7 +7798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7851,7 +7841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45629</v>
+        <v>45692</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7881,7 +7871,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7924,7 +7914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7938,10 +7928,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45629</v>
+        <v>44951</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7953,8 +7943,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7997,7 +7992,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8007,14 +8002,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44583</v>
+        <v>44924</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8089,10 +8084,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46210</v>
+        <v>44583</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8104,8 +8099,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8158,14 +8158,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45628</v>
+        <v>46203</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46216</v>
+        <v>45387</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>13.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46216</v>
+        <v>46210</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46216</v>
+        <v>45629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8454,10 +8454,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46216</v>
+        <v>44905</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8469,8 +8469,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8513,7 +8518,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8523,14 +8528,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44673</v>
+        <v>44851</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8543,7 +8548,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8586,7 +8591,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8600,10 +8605,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45692</v>
+        <v>46216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8616,7 +8621,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>11.2</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8659,7 +8664,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8673,10 +8678,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44935</v>
+        <v>44673</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8689,7 +8694,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8732,7 +8737,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8746,10 +8751,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45166</v>
+        <v>46216</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8762,7 +8767,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8805,7 +8810,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8819,10 +8824,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45300</v>
+        <v>46216</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8835,7 +8840,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>10.1</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8878,7 +8883,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45155</v>
+        <v>46216</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8908,7 +8913,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8951,7 +8956,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8965,10 +8970,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45811</v>
+        <v>44677</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8981,7 +8986,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9024,7 +9029,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9038,10 +9043,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45842</v>
+        <v>44952</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9055,11 +9060,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9102,7 +9107,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9116,10 +9121,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45861</v>
+        <v>44920</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9131,13 +9136,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 3914-2023</t>
+          <t>A 31523-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44952</v>
+        <v>44775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,16 +1593,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1611,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1623,21 +1618,138 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1645,148 +1757,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 12620-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45817</v>
+        <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1971,481 +1971,481 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 12620-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 31575-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45499</v>
+        <v>44775</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,13 +2809,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2824,10 +2819,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2842,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2851,153 +2846,158 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 30949-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45834</v>
+        <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,20 +3027,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3063,46 +3063,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44915</v>
+        <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3168,39 +3168,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44523</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>44851</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>45476</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4895,8 +4895,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4939,7 +4944,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4953,10 +4958,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4968,8 +4973,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5012,7 +5022,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5026,10 +5036,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45155</v>
+        <v>45447</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5041,8 +5051,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5085,7 +5100,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5099,10 +5114,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44951</v>
+        <v>44673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5114,13 +5129,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5163,7 +5173,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5173,14 +5183,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45518</v>
+        <v>44917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5193,7 +5203,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5236,7 +5246,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5250,10 +5260,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45811</v>
+        <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5265,8 +5275,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5309,7 +5324,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5323,10 +5338,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45756</v>
+        <v>46087</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5359,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5404,7 +5419,7 @@
         <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5465,7 +5480,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5479,10 +5494,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44915</v>
+        <v>44952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5494,8 +5509,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5555,7 +5575,7 @@
         <v>45861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5616,7 +5636,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5626,14 +5646,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44673</v>
+        <v>44924</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5643,6 +5663,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5689,7 +5714,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5699,14 +5724,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44935</v>
+        <v>45783</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5719,7 +5744,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5762,7 +5787,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5776,10 +5801,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44917</v>
+        <v>45995</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5792,7 +5817,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5835,7 +5860,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5849,10 +5874,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46049</v>
+        <v>45043</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5865,7 +5890,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5908,7 +5933,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5918,14 +5943,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45953</v>
+        <v>45848</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5938,7 +5963,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5981,7 +6006,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5995,10 +6020,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6016,7 +6041,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6059,7 +6084,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6073,10 +6098,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45476</v>
+        <v>45450</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6094,7 +6119,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6137,7 +6162,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6151,10 +6176,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45397</v>
+        <v>44678</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6167,7 +6192,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>13.6</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6210,7 +6235,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6220,14 +6245,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46087</v>
+        <v>45518</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6237,11 +6262,6 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -6288,7 +6308,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6302,10 +6322,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45166</v>
+        <v>45842</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6317,8 +6337,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6361,7 +6386,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6375,10 +6400,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44673</v>
+        <v>45387</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6391,7 +6416,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>13.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6434,7 +6459,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6448,10 +6473,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44565</v>
+        <v>44915</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6463,13 +6488,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6512,7 +6532,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6522,14 +6542,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45848</v>
+        <v>46161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6542,7 +6562,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6585,7 +6605,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6599,10 +6619,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45995</v>
+        <v>44920</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6615,7 +6635,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6658,7 +6678,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6672,10 +6692,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45783</v>
+        <v>45716</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6688,7 +6708,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6748,7 +6768,7 @@
         <v>44966</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6804,7 +6824,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6814,14 +6834,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45043</v>
+        <v>46182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6834,7 +6854,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6877,7 +6897,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6887,14 +6907,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45628</v>
+        <v>45953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6907,7 +6927,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6950,7 +6970,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6964,10 +6984,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45450</v>
+        <v>45113</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6979,13 +6999,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7028,7 +7043,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7042,10 +7057,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44678</v>
+        <v>45629</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7058,7 +7073,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7101,7 +7116,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7115,10 +7130,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45300</v>
+        <v>45629</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7131,7 +7146,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>10.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7174,7 +7189,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7188,10 +7203,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45842</v>
+        <v>44583</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7209,7 +7224,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7252,7 +7267,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7262,14 +7277,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45113</v>
+        <v>45628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7282,7 +7297,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7325,7 +7340,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7335,14 +7350,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46161</v>
+        <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7355,7 +7370,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>13.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7398,7 +7413,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7408,14 +7423,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45716</v>
+        <v>44673</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7443,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7471,7 +7486,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7485,10 +7500,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45719</v>
+        <v>44905</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7500,8 +7515,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7544,7 +7564,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7554,14 +7574,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46182</v>
+        <v>45719</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7594,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7617,7 +7637,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7631,10 +7651,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45082</v>
+        <v>46210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7667,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7690,7 +7710,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7704,10 +7724,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45476</v>
+        <v>46216</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7719,13 +7739,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7768,7 +7783,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7782,10 +7797,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45629</v>
+        <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7798,7 +7813,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7841,7 +7856,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7855,10 +7870,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45692</v>
+        <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7871,7 +7886,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>11.2</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7914,7 +7929,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7928,10 +7943,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44951</v>
+        <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7943,13 +7958,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7992,7 +8002,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8002,14 +8012,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44924</v>
+        <v>44673</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8019,11 +8029,6 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -8070,7 +8075,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8084,10 +8089,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44583</v>
+        <v>45397</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8099,13 +8104,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>13.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46203</v>
+        <v>44915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>13.8</v>
+        <v>3.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45387</v>
+        <v>44951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8250,8 +8250,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>13.7</v>
+        <v>4.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8294,7 +8299,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8308,10 +8313,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46210</v>
+        <v>44951</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8323,8 +8328,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8367,7 +8377,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8381,10 +8391,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45629</v>
+        <v>45082</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8397,7 +8407,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8440,7 +8450,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8454,10 +8464,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44905</v>
+        <v>44677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8469,13 +8479,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8518,7 +8523,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8532,10 +8537,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44851</v>
+        <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8548,7 +8553,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8591,7 +8596,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8605,10 +8610,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46216</v>
+        <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8621,7 +8626,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8664,7 +8669,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8674,14 +8679,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44673</v>
+        <v>44937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8694,7 +8699,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8737,7 +8742,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8751,10 +8756,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46216</v>
+        <v>45692</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8767,7 +8772,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>11.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8810,7 +8815,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8820,14 +8825,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46216</v>
+        <v>44935</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8840,7 +8845,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8883,7 +8888,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8897,10 +8902,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46216</v>
+        <v>45166</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8913,7 +8918,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8956,7 +8961,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8970,10 +8975,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44677</v>
+        <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8986,7 +8991,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9029,7 +9034,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9043,10 +9048,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44952</v>
+        <v>45155</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9058,13 +9063,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44920</v>
+        <v>45811</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,11 +1593,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1606,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1618,21 +1623,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1640,153 +1757,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 61363-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2129,14 +2129,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45618</v>
+        <v>44915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,17 +2149,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2182,159 +2182,159 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>6</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,8 +2809,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2819,10 +2824,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2837,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2846,151 +2851,146 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,17 +3132,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3172,42 +3172,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46008</v>
+        <v>44523</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3236,18 +3236,23 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3261,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3273,46 +3278,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3329,7 +3338,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,16 +3351,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3366,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3382,42 +3391,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3431,10 +3440,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44523</v>
+        <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3446,13 +3455,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3461,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3476,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3488,43 +3492,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44851</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4895,13 +4895,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4944,7 +4939,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4958,10 +4953,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4973,13 +4968,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5022,7 +5012,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5036,10 +5026,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45447</v>
+        <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5051,13 +5041,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5100,7 +5085,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5114,10 +5099,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44673</v>
+        <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5129,8 +5114,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5173,7 +5163,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5183,14 +5173,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44917</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5203,7 +5193,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5263,7 +5253,7 @@
         <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5324,7 +5314,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5338,10 +5328,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46087</v>
+        <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5353,13 +5343,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5402,7 +5387,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5416,10 +5401,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45842</v>
+        <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5431,13 +5416,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5480,7 +5460,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5494,10 +5474,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44952</v>
+        <v>44917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5509,13 +5489,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5558,7 +5533,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5568,14 +5543,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45861</v>
+        <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5587,13 +5562,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5636,7 +5606,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5646,14 +5616,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44924</v>
+        <v>45447</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5671,7 +5641,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5714,7 +5684,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5728,10 +5698,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45783</v>
+        <v>45476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5743,8 +5713,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5787,7 +5762,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5801,10 +5776,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45995</v>
+        <v>45848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5817,7 +5792,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5860,7 +5835,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5874,10 +5849,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45043</v>
+        <v>45995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5890,7 +5865,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5933,7 +5908,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5947,10 +5922,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45848</v>
+        <v>45783</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5963,7 +5938,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6006,7 +5981,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6020,10 +5995,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44565</v>
+        <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6035,13 +6010,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>13.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6084,7 +6054,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6098,10 +6068,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45450</v>
+        <v>45043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6113,13 +6083,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6162,7 +6127,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6176,10 +6141,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44678</v>
+        <v>45166</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6192,7 +6157,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6235,7 +6200,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6245,14 +6210,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45518</v>
+        <v>45450</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6264,8 +6229,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6308,7 +6278,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6322,10 +6292,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45842</v>
+        <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6337,13 +6307,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6386,7 +6351,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6400,10 +6365,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45387</v>
+        <v>44565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6415,8 +6380,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>13.7</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6459,7 +6429,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6473,10 +6443,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44915</v>
+        <v>44678</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6489,7 +6459,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6532,7 +6502,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6546,10 +6516,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46161</v>
+        <v>45953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6562,7 +6532,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6605,7 +6575,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6619,10 +6589,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44920</v>
+        <v>45842</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6634,8 +6604,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6678,7 +6653,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6692,10 +6667,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45716</v>
+        <v>44966</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6708,7 +6683,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6751,7 +6726,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6761,14 +6736,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44966</v>
+        <v>45628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6781,7 +6756,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6824,7 +6799,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6838,10 +6813,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46182</v>
+        <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6854,7 +6829,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6897,7 +6872,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6907,14 +6882,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45953</v>
+        <v>45716</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6927,7 +6902,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6970,7 +6945,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6984,10 +6959,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45113</v>
+        <v>45300</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7000,7 +6975,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>10.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7043,7 +7018,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7057,10 +7032,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45629</v>
+        <v>45113</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7073,7 +7048,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7116,7 +7091,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7130,10 +7105,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45629</v>
+        <v>46049</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7146,7 +7121,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7189,7 +7164,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7203,10 +7178,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44583</v>
+        <v>45719</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7218,13 +7193,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7267,7 +7237,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7277,14 +7247,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45628</v>
+        <v>46182</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7297,7 +7267,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7340,7 +7310,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7354,10 +7324,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46203</v>
+        <v>46087</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7369,8 +7339,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>13.8</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7413,7 +7388,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7423,14 +7398,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44673</v>
+        <v>45082</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7443,7 +7418,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7486,7 +7461,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7500,10 +7475,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44905</v>
+        <v>45476</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7517,11 +7492,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7564,7 +7539,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7578,10 +7553,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45719</v>
+        <v>45629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7594,7 +7569,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7637,7 +7612,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7651,10 +7626,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46210</v>
+        <v>45692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7667,7 +7642,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7710,7 +7685,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7724,10 +7699,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46216</v>
+        <v>44951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7739,8 +7714,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7783,7 +7763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,14 +7773,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46216</v>
+        <v>44924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,8 +7792,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7856,7 +7841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7870,10 +7855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46216</v>
+        <v>44583</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,8 +7870,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7929,7 +7919,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7943,10 +7933,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46216</v>
+        <v>45387</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7959,7 +7949,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>13.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8002,7 +7992,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8016,10 +8006,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44673</v>
+        <v>46203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8032,7 +8022,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>13.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8075,7 +8065,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8089,10 +8079,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45397</v>
+        <v>45629</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8105,7 +8095,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>13.6</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8162,10 +8152,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44915</v>
+        <v>44905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8177,8 +8167,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44951</v>
+        <v>44851</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8250,13 +8245,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8299,7 +8289,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8309,14 +8299,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44951</v>
+        <v>44673</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8328,13 +8318,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8377,7 +8362,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8391,10 +8376,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45082</v>
+        <v>44677</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8407,7 +8392,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.1</v>
+        <v>5.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8450,7 +8435,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8464,10 +8449,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44677</v>
+        <v>46210</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8480,7 +8465,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8523,7 +8508,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8537,10 +8522,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46049</v>
+        <v>44952</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8552,8 +8537,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8596,7 +8586,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8610,10 +8600,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44937</v>
+        <v>46216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8626,7 +8616,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8669,7 +8659,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8683,10 +8673,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44937</v>
+        <v>46216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8699,7 +8689,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8742,7 +8732,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8756,10 +8746,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45692</v>
+        <v>46216</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8772,7 +8762,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8815,7 +8805,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8825,14 +8815,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44935</v>
+        <v>44920</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8845,7 +8835,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8888,7 +8878,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8902,10 +8892,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45166</v>
+        <v>46216</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8918,7 +8908,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8961,7 +8951,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8975,10 +8965,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>45811</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8991,7 +8981,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9034,7 +9024,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9048,10 +9038,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45155</v>
+        <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9063,8 +9053,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9107,7 +9102,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9121,10 +9116,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45811</v>
+        <v>45861</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9136,8 +9131,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44775</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>44523</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45447</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45783</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45166</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45450</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44678</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>45953</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>45842</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44966</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>45716</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>45300</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45113</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>46049</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45719</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>46182</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>46087</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45082</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45476</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>44583</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45387</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>46203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45629</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44851</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44673</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44677</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>46210</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>44952</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>46216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>46216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46216</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44920</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>46216</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>45811</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45861</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44775</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44523</v>
+        <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3236,22 +3236,17 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3266,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3278,50 +3273,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3335,10 +3326,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46008</v>
+        <v>44523</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3350,18 +3341,23 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3375,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3387,39 +3383,43 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
         <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45447</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45783</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45397</v>
+        <v>45043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>13.6</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6054,7 +6054,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45043</v>
+        <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45166</v>
+        <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6156,8 +6156,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6200,7 +6205,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6214,10 +6219,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45450</v>
+        <v>44678</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6229,13 +6234,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44673</v>
+        <v>45842</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6307,8 +6307,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6351,7 +6356,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6361,14 +6366,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44565</v>
+        <v>45953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6380,13 +6385,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44678</v>
+        <v>45166</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6502,7 +6502,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6512,14 +6512,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45953</v>
+        <v>44673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45842</v>
+        <v>44565</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6663,14 +6663,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44966</v>
+        <v>46161</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6726,7 +6726,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6736,14 +6736,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45628</v>
+        <v>45716</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6799,7 +6799,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46161</v>
+        <v>44966</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6882,14 +6882,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45716</v>
+        <v>46182</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6945,7 +6945,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45300</v>
+        <v>46049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10.1</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7028,14 +7028,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45113</v>
+        <v>45628</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7091,7 +7091,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46049</v>
+        <v>45300</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>10.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7164,7 +7164,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45719</v>
+        <v>46087</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7193,8 +7193,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7237,7 +7242,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7247,14 +7252,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46182</v>
+        <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7267,7 +7272,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.9</v>
+        <v>13.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7310,7 +7315,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7324,10 +7329,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46087</v>
+        <v>45113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7339,13 +7344,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45082</v>
+        <v>45719</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45476</v>
+        <v>46210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7490,13 +7490,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7539,7 +7534,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7553,10 +7548,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45629</v>
+        <v>45082</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7569,7 +7564,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7612,7 +7607,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7626,10 +7621,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45692</v>
+        <v>45476</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7641,8 +7636,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>11.2</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44951</v>
+        <v>46216</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7714,13 +7714,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7763,7 +7758,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7773,14 +7768,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44924</v>
+        <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7792,13 +7787,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7841,7 +7831,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7855,10 +7845,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44583</v>
+        <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7870,13 +7860,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7919,7 +7904,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7933,10 +7918,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45387</v>
+        <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7949,7 +7934,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>13.7</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7992,7 +7977,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8006,10 +7991,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46203</v>
+        <v>45629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8022,7 +8007,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>13.8</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8065,7 +8050,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8079,10 +8064,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45629</v>
+        <v>45692</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8095,7 +8080,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>11.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8138,7 +8123,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8152,10 +8137,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44905</v>
+        <v>44951</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8216,7 +8201,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8226,14 +8211,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44851</v>
+        <v>44924</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8245,8 +8230,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8289,7 +8279,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8299,14 +8289,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44673</v>
+        <v>44583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8318,8 +8308,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8362,7 +8357,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8376,10 +8371,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44677</v>
+        <v>45387</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8392,7 +8387,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>13.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8435,7 +8430,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8449,10 +8444,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46210</v>
+        <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8465,7 +8460,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8508,7 +8503,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8522,10 +8517,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44952</v>
+        <v>44905</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8543,7 +8538,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8586,7 +8581,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8600,10 +8595,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46216</v>
+        <v>44851</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8616,7 +8611,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8659,7 +8654,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8669,14 +8664,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46216</v>
+        <v>44673</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8689,7 +8684,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8732,7 +8727,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8746,10 +8741,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46216</v>
+        <v>44677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8762,7 +8757,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8805,7 +8800,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44920</v>
+        <v>44952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8834,8 +8829,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46216</v>
+        <v>44920</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8968,7 +8968,7 @@
         <v>45811</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45861</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 3914-2023</t>
+          <t>A 31523-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44952</v>
+        <v>44775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,16 +1593,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1611,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1623,21 +1618,138 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1645,148 +1757,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62578-2025</t>
+          <t>A 27948-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46007</v>
+        <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,19 +2042,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2066,386 +2066,386 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Mindre märgborre
 Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 61363-2022</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44915</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>5.3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 31575-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45499</v>
+        <v>44775</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,13 +2809,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2824,10 +2819,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2842,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2851,146 +2846,151 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 30949-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46008</v>
+        <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3172,35 +3172,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44523</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,17 +3456,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3496,35 +3496,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44747</v>
+        <v>44924</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4749,8 +4749,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4793,7 +4798,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4807,10 +4812,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4823,7 +4828,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4866,7 +4871,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4880,10 +4885,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>44565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4895,8 +4900,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4939,7 +4949,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4953,10 +4963,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>44851</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4969,7 +4979,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5012,7 +5022,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5022,14 +5032,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45155</v>
+        <v>45518</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5042,7 +5052,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5085,7 +5095,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5099,10 +5109,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44951</v>
+        <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5114,13 +5124,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>13.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5163,7 +5168,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5173,14 +5178,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45518</v>
+        <v>44915</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5193,7 +5198,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5236,7 +5241,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5250,10 +5255,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45756</v>
+        <v>45476</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5276,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5314,7 +5319,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5328,10 +5333,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44915</v>
+        <v>44920</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5349,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5387,7 +5392,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5401,10 +5406,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44673</v>
+        <v>44966</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5460,7 +5465,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5474,10 +5479,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44917</v>
+        <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5489,8 +5494,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5533,7 +5543,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5543,14 +5553,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44935</v>
+        <v>45447</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5562,8 +5572,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5606,7 +5621,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5620,10 +5635,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45447</v>
+        <v>45811</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5635,13 +5650,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5684,7 +5694,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5698,10 +5708,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45476</v>
+        <v>44673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5713,13 +5723,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5762,7 +5767,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5776,10 +5781,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45848</v>
+        <v>45113</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5792,7 +5797,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5835,7 +5840,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5849,10 +5854,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45995</v>
+        <v>45629</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5865,7 +5870,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5908,7 +5913,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5922,10 +5927,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45783</v>
+        <v>45629</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5938,7 +5943,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5981,7 +5986,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5995,10 +6000,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45043</v>
+        <v>44917</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6011,7 +6016,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6054,7 +6059,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6064,14 +6069,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45397</v>
+        <v>45953</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6084,7 +6089,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>13.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6127,7 +6132,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6141,10 +6146,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45450</v>
+        <v>45756</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6162,7 +6167,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6205,7 +6210,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44678</v>
+        <v>44583</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6234,8 +6239,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6278,7 +6288,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6288,14 +6298,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45842</v>
+        <v>45628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6307,13 +6317,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6356,7 +6361,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6366,14 +6371,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45953</v>
+        <v>44952</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6385,8 +6390,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6429,7 +6439,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6439,14 +6449,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45166</v>
+        <v>44673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6459,7 +6469,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6502,7 +6512,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6516,10 +6526,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44673</v>
+        <v>44905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6531,8 +6541,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6575,7 +6590,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6589,10 +6604,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44565</v>
+        <v>45719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6604,13 +6619,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6653,7 +6663,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6663,14 +6673,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46161</v>
+        <v>44673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6683,7 +6693,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6726,7 +6736,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6740,10 +6750,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45716</v>
+        <v>45397</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6756,7 +6766,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>13.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6799,7 +6809,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6813,10 +6823,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44966</v>
+        <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6829,7 +6839,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6872,7 +6882,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6882,14 +6892,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46182</v>
+        <v>45842</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6901,8 +6911,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6945,7 +6960,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6959,10 +6974,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46049</v>
+        <v>44915</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6975,7 +6990,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7018,7 +7033,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7028,14 +7043,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45628</v>
+        <v>44951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7047,8 +7062,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7091,7 +7111,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7105,10 +7125,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45300</v>
+        <v>44951</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7120,8 +7140,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>10.1</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7181,7 +7206,7 @@
         <v>46087</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7242,7 +7267,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7256,10 +7281,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46203</v>
+        <v>45082</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7272,7 +7297,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.8</v>
+        <v>0.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7315,7 +7340,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7329,10 +7354,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45113</v>
+        <v>44677</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7345,7 +7370,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7388,7 +7413,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7402,10 +7427,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45719</v>
+        <v>45861</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7417,8 +7442,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7461,7 +7491,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7475,10 +7505,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46210</v>
+        <v>44937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7491,7 +7521,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7534,7 +7564,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7548,10 +7578,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45082</v>
+        <v>44937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7564,7 +7594,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7607,7 +7637,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7621,10 +7651,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45476</v>
+        <v>45783</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7636,13 +7666,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7685,7 +7710,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7699,10 +7724,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46216</v>
+        <v>45995</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7715,7 +7740,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7758,7 +7783,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7772,10 +7797,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46216</v>
+        <v>45043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7788,7 +7813,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7831,7 +7856,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7845,10 +7870,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46216</v>
+        <v>45692</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7861,7 +7886,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7904,7 +7929,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7914,14 +7939,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46216</v>
+        <v>44935</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7934,7 +7959,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7977,7 +8002,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7991,10 +8016,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45629</v>
+        <v>45166</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8007,7 +8032,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8050,7 +8075,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8064,10 +8089,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45692</v>
+        <v>45848</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8080,7 +8105,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8123,7 +8148,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8137,10 +8162,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44951</v>
+        <v>45300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8152,13 +8177,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>4.7</v>
+        <v>10.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8201,7 +8221,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8211,14 +8231,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44924</v>
+        <v>45155</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8230,13 +8250,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8279,7 +8294,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8293,10 +8308,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44583</v>
+        <v>45450</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8314,7 +8329,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8357,7 +8372,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8371,10 +8386,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45387</v>
+        <v>44678</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8387,7 +8402,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>13.7</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8430,7 +8445,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8444,10 +8459,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45629</v>
+        <v>45842</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8459,8 +8474,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8503,7 +8523,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8513,14 +8533,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44905</v>
+        <v>46161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8532,13 +8552,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8581,7 +8596,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8595,10 +8610,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44851</v>
+        <v>45716</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8611,7 +8626,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8654,7 +8669,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8668,10 +8683,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44673</v>
+        <v>46182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8684,7 +8699,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8727,7 +8742,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8741,10 +8756,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44677</v>
+        <v>46203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8757,7 +8772,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.9</v>
+        <v>13.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8800,7 +8815,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8814,10 +8829,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44952</v>
+        <v>46210</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8829,13 +8844,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8878,7 +8888,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8892,10 +8902,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44920</v>
+        <v>46216</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8908,7 +8918,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8951,7 +8961,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8965,10 +8975,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45811</v>
+        <v>46216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8981,7 +8991,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9024,7 +9034,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9038,10 +9048,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45842</v>
+        <v>46216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9053,13 +9063,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9102,7 +9107,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9116,10 +9121,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45861</v>
+        <v>46216</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9131,13 +9136,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,11 +1593,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1606,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1618,21 +1623,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1640,153 +1757,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 62578-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45817</v>
+        <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,19 +2042,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2066,386 +2066,386 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,8 +2809,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2819,10 +2824,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2837,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2846,151 +2851,146 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,17 +3132,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3172,35 +3172,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44523</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46008</v>
+        <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,16 +3456,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3496,35 +3496,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4216,7 +4216,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44924</v>
+        <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4749,13 +4749,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4798,7 +4793,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4812,10 +4807,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44747</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4828,7 +4823,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4871,7 +4866,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4885,10 +4880,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44565</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4900,13 +4895,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4949,7 +4939,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4963,10 +4953,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44851</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4969,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5022,7 +5012,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5032,14 +5022,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45518</v>
+        <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5042,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5095,7 +5085,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5109,10 +5099,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45387</v>
+        <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5124,8 +5114,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>13.7</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5168,7 +5163,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5178,14 +5173,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44915</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5193,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5241,7 +5236,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45476</v>
+        <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5276,7 +5271,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5319,7 +5314,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5333,10 +5328,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44920</v>
+        <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5349,7 +5344,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5392,7 +5387,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5406,10 +5401,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44966</v>
+        <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5465,7 +5460,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5479,10 +5474,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45476</v>
+        <v>44917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5494,13 +5489,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5543,7 +5533,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5553,14 +5543,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45447</v>
+        <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5572,13 +5562,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5621,7 +5606,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5635,10 +5620,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45811</v>
+        <v>45447</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5650,8 +5635,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5694,7 +5684,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5708,10 +5698,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44673</v>
+        <v>45476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5723,8 +5713,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5767,7 +5762,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5781,10 +5776,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45113</v>
+        <v>45848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5797,7 +5792,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5840,7 +5835,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5854,10 +5849,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45629</v>
+        <v>45995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5870,7 +5865,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5913,7 +5908,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5927,10 +5922,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45629</v>
+        <v>45397</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5943,7 +5938,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>13.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5986,7 +5981,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6000,10 +5995,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44917</v>
+        <v>45783</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6016,7 +6011,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6059,7 +6054,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6069,14 +6064,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45953</v>
+        <v>45166</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6089,7 +6084,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6132,7 +6127,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6146,10 +6141,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45756</v>
+        <v>45043</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6161,13 +6156,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6210,7 +6200,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6220,14 +6210,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44583</v>
+        <v>45953</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6239,13 +6229,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6288,7 +6273,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6298,14 +6283,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45628</v>
+        <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6318,7 +6303,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6361,7 +6346,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6375,10 +6360,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44952</v>
+        <v>44565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6392,11 +6377,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6439,7 +6424,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6449,14 +6434,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44673</v>
+        <v>45450</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6468,8 +6453,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6512,7 +6502,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6526,10 +6516,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44905</v>
+        <v>44678</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6541,13 +6531,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6590,7 +6575,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6604,10 +6589,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45719</v>
+        <v>45842</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6619,8 +6604,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6663,7 +6653,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6677,10 +6667,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44673</v>
+        <v>44966</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6693,7 +6683,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6736,7 +6726,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6746,14 +6736,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45397</v>
+        <v>45628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6766,7 +6756,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>13.6</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6826,7 +6816,7 @@
         <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6882,7 +6872,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6892,14 +6882,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45842</v>
+        <v>46161</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6911,13 +6901,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6960,7 +6945,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6974,10 +6959,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44915</v>
+        <v>45716</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6990,7 +6975,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7033,7 +7018,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7047,10 +7032,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44951</v>
+        <v>45300</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7062,13 +7047,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>10.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7111,7 +7091,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7125,10 +7105,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44951</v>
+        <v>46087</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7142,11 +7122,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7189,7 +7169,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7203,10 +7183,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46087</v>
+        <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7218,13 +7198,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7267,7 +7242,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7277,14 +7252,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45082</v>
+        <v>46182</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7297,7 +7272,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7340,7 +7315,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7354,10 +7329,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44677</v>
+        <v>45719</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7370,7 +7345,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7413,7 +7388,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7427,10 +7402,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45861</v>
+        <v>45082</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7442,13 +7417,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7491,7 +7461,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7505,10 +7475,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44937</v>
+        <v>46203</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7521,7 +7491,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>13.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7564,7 +7534,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7578,10 +7548,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44937</v>
+        <v>45476</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7593,8 +7563,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7637,7 +7612,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7651,10 +7626,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45783</v>
+        <v>45629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7667,7 +7642,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7710,7 +7685,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7724,10 +7699,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45995</v>
+        <v>45692</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7740,7 +7715,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>11.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7783,7 +7758,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7797,10 +7772,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45043</v>
+        <v>44951</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,8 +7787,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7856,7 +7836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7866,14 +7846,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45692</v>
+        <v>44924</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,8 +7865,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7929,7 +7914,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7939,14 +7924,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44935</v>
+        <v>44583</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7958,8 +7943,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8002,7 +7992,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8016,10 +8006,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45166</v>
+        <v>46210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8032,7 +8022,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8075,7 +8065,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8089,10 +8079,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45848</v>
+        <v>45387</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8105,7 +8095,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>13.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8162,10 +8152,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45300</v>
+        <v>46216</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8178,7 +8168,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>10.1</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8221,7 +8211,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8235,10 +8225,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45155</v>
+        <v>45629</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8251,7 +8241,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8294,7 +8284,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8308,10 +8298,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45450</v>
+        <v>44905</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8325,7 +8315,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -8372,7 +8362,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8386,10 +8376,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44678</v>
+        <v>46216</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8402,7 +8392,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8445,7 +8435,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45842</v>
+        <v>46216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8474,13 +8464,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8523,7 +8508,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8533,14 +8518,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46161</v>
+        <v>44851</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8553,7 +8538,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8596,7 +8581,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8610,10 +8595,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45716</v>
+        <v>46216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8626,7 +8611,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8669,7 +8654,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8683,10 +8668,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46182</v>
+        <v>44673</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8699,7 +8684,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8742,7 +8727,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8756,10 +8741,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46203</v>
+        <v>44677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8772,7 +8757,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>13.8</v>
+        <v>5.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8815,7 +8800,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8829,10 +8814,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46210</v>
+        <v>44952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8844,8 +8829,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8888,7 +8878,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8902,10 +8892,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46216</v>
+        <v>44920</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8918,7 +8908,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8961,7 +8951,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8975,10 +8965,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46216</v>
+        <v>45811</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8991,7 +8981,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9034,7 +9024,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9048,10 +9038,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46216</v>
+        <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9063,8 +9053,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9107,7 +9102,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9121,10 +9116,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46216</v>
+        <v>45861</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9136,8 +9131,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
         <v>45302</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE105"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 3914-2023</t>
+          <t>A 39926-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44952</v>
+        <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,17 +1595,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>15.3</v>
+        <v>9.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1629,15 +1629,242 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Nästlav
+Skogsbräsma
+Skogsknipprot
+Kungsfågel
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 39926-2026 artfynd.xlsx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 39926-2026 karta.png", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 39926-2026 georefererad karta.tif", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 39926-2026 FSC-klagomål.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 39926-2026 FSC-klagomål mail.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 39926-2026 tillsynsbegäran.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 39926-2026 tillsynsbegäran mail.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1645,223 +1872,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 37244-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="D13" s="1" t="n">
+        <v>45540</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 37244-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Talltita
@@ -1869,1240 +1984,1135 @@
 Grovticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 12620-2022</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>44638</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Taggfingersvamp
 Fällmossa
 Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="D18" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 67244-2021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="D19" s="1" t="n">
+        <v>44523</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 67244-2021</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44523</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Backdvärgmal</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67244-2021 artfynd.xlsx", "A 67244-2021")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67244-2021 karta.png", "A 67244-2021")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67244-2021 georefererad karta.tif", "A 67244-2021")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67244-2021 FSC-klagomål.docx", "A 67244-2021")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67244-2021 FSC-klagomål mail.docx", "A 67244-2021")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67244-2021 tillsynsbegäran.docx", "A 67244-2021")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67244-2021 tillsynsbegäran mail.docx", "A 67244-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 61275-2021</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>44498</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>2.1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Nattviol</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61275-2021 artfynd.xlsx", "A 61275-2021")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61275-2021 karta.png", "A 61275-2021")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61275-2021 georefererad karta.tif", "A 61275-2021")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61275-2021 FSC-klagomål.docx", "A 61275-2021")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61275-2021 FSC-klagomål mail.docx", "A 61275-2021")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61275-2021 tillsynsbegäran.docx", "A 61275-2021")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61275-2021 tillsynsbegäran mail.docx", "A 61275-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 43308-2024</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45568</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>3.2</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallticka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 30949-2024</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45499</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>3.2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 61323-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Gulvit blekspik</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3116,10 +3126,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46008</v>
+        <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3142,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3141,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3159,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3168,39 +3178,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3234,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3322,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3326,10 +3336,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44523</v>
+        <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,16 +3351,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3383,43 +3388,39 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
@@ -3443,7 +3444,7 @@
         <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,24 +3532,24 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S 5861-2022</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44852</v>
+        <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,23 +3561,28 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3588,55 +3594,59 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 5861-2022 artfynd.xlsx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 5861-2022 karta.png", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 5861-2022 georefererad karta.tif", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 5861-2022 FSC-klagomål.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 5861-2022 FSC-klagomål mail.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 5861-2022 tillsynsbegäran.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 5861-2022 tillsynsbegäran mail.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S 15-2025</t>
+          <t>S 5861-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3650,10 +3660,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45660</v>
+        <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3665,13 +3675,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3683,10 +3688,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3704,66 +3709,66 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 15-2025 artfynd.xlsx", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 5861-2022 artfynd.xlsx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 15-2025 karta.png", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 5861-2022 karta.png", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 15-2025 georefererad karta.tif", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 5861-2022 georefererad karta.tif", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 15-2025 FSC-klagomål.docx", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 5861-2022 FSC-klagomål.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 15-2025 FSC-klagomål mail.docx", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 5861-2022 FSC-klagomål mail.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 15-2025 tillsynsbegäran.docx", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 5861-2022 tillsynsbegäran.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 15-2025 tillsynsbegäran mail.docx", "S 15-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 5861-2022 tillsynsbegäran mail.docx", "S 5861-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2148-2022</t>
+          <t>S 15-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44575</v>
+        <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3786,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3793,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3805,26 +3810,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 15-2025 artfynd.xlsx", "S 15-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 15-2025 karta.png", "S 15-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 15-2025 georefererad karta.tif", "S 15-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 15-2025 FSC-klagomål.docx", "S 15-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 15-2025 FSC-klagomål mail.docx", "S 15-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 15-2025 tillsynsbegäran.docx", "S 15-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 15-2025 tillsynsbegäran mail.docx", "S 15-2025")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1910-2022</t>
+          <t>A 2148-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3841,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3859,7 +3896,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3902,7 +3939,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 72508-2021</t>
+          <t>A 1910-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3916,10 +3953,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44544</v>
+        <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3937,7 +3974,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3980,7 +4017,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15131-2022</t>
+          <t>A 72508-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3994,10 +4031,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44658</v>
+        <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4009,8 +4046,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4053,7 +4095,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19934-2022</t>
+          <t>A 15131-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4067,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44697</v>
+        <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4083,7 +4125,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4126,7 +4168,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19944-2022</t>
+          <t>A 19934-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4143,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4156,7 +4198,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4199,7 +4241,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 19944-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4213,10 +4255,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44569</v>
+        <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4228,13 +4270,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4294,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4355,7 +4392,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28405-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4369,10 +4406,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44747</v>
+        <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4384,8 +4421,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4428,7 +4470,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17173-2022</t>
+          <t>A 28405-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4442,10 +4484,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44677</v>
+        <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4458,7 +4500,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4501,7 +4543,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10082-2022</t>
+          <t>A 17173-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4515,10 +4557,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44621</v>
+        <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4531,7 +4573,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4574,7 +4616,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28964-2022</t>
+          <t>A 10082-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4588,10 +4630,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44749</v>
+        <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4604,7 +4646,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4647,7 +4689,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18091-2022</t>
+          <t>A 28964-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4661,10 +4703,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44684</v>
+        <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4677,7 +4719,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4720,7 +4762,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 18091-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4734,10 +4776,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44747</v>
+        <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4750,7 +4792,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4793,7 +4835,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4807,10 +4849,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4823,7 +4865,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4866,7 +4908,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4880,10 +4922,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>44851</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4896,7 +4938,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4939,7 +4981,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4953,10 +4995,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4968,8 +5010,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5012,7 +5059,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5026,10 +5073,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45155</v>
+        <v>46049</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5042,7 +5089,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5085,7 +5132,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5099,10 +5146,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44951</v>
+        <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5116,11 +5163,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5163,7 +5210,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5173,14 +5220,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45518</v>
+        <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5192,8 +5239,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5236,7 +5288,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5250,10 +5302,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45756</v>
+        <v>44673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5265,13 +5317,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5314,7 +5361,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5328,10 +5375,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44915</v>
+        <v>44917</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5391,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5387,7 +5434,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5401,10 +5448,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44673</v>
+        <v>46087</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5416,8 +5463,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5460,7 +5512,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5474,10 +5526,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44917</v>
+        <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5489,8 +5541,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5533,7 +5590,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5547,10 +5604,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44935</v>
+        <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5563,7 +5620,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5606,7 +5663,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5620,10 +5677,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45447</v>
+        <v>44952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5637,11 +5694,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5684,7 +5741,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5698,10 +5755,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45476</v>
+        <v>45811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5713,13 +5770,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5762,7 +5814,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5776,10 +5828,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45848</v>
+        <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5792,7 +5844,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5835,7 +5887,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5845,14 +5897,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45995</v>
+        <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5864,8 +5916,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5908,7 +5965,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5922,10 +5979,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45397</v>
+        <v>45995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5938,7 +5995,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.6</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5981,7 +6038,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5995,10 +6052,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45783</v>
+        <v>45043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6011,7 +6068,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6054,7 +6111,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6068,10 +6125,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45166</v>
+        <v>45848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6084,7 +6141,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6127,7 +6184,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6141,10 +6198,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45043</v>
+        <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6156,8 +6213,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6200,7 +6262,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6210,14 +6272,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45953</v>
+        <v>44678</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6230,7 +6292,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6273,7 +6335,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6287,10 +6349,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44673</v>
+        <v>44565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6302,8 +6364,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6346,7 +6413,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6360,10 +6427,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44565</v>
+        <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6381,7 +6448,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6424,7 +6491,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6434,14 +6501,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45450</v>
+        <v>45518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6453,13 +6520,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6502,7 +6564,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6516,10 +6578,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44678</v>
+        <v>45842</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6531,8 +6593,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6575,7 +6642,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6585,14 +6652,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45842</v>
+        <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6604,13 +6671,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6653,7 +6715,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6667,10 +6729,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44966</v>
+        <v>45387</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6683,7 +6745,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>13.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6726,7 +6788,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6736,14 +6798,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45628</v>
+        <v>44915</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6756,7 +6818,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6799,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6813,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46049</v>
+        <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6829,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6872,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6882,14 +6944,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46161</v>
+        <v>45861</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6901,8 +6963,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6945,7 +7012,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6959,10 +7026,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45716</v>
+        <v>44920</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6975,7 +7042,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7018,7 +7085,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7028,14 +7095,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45300</v>
+        <v>46182</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7048,7 +7115,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.1</v>
+        <v>4.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7091,7 +7158,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7105,10 +7172,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46087</v>
+        <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7120,13 +7187,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7186,7 +7248,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7242,7 +7304,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7252,14 +7314,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46182</v>
+        <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7272,7 +7334,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7315,7 +7377,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7329,10 +7391,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45719</v>
+        <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7345,7 +7407,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7388,7 +7450,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7402,10 +7464,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45082</v>
+        <v>46203</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7418,7 +7480,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.1</v>
+        <v>13.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7461,7 +7523,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7475,10 +7537,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46203</v>
+        <v>44583</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7490,8 +7552,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>13.8</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7534,7 +7601,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7544,14 +7611,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45476</v>
+        <v>45628</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7563,13 +7630,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7612,7 +7674,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7626,10 +7688,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45629</v>
+        <v>46210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7642,7 +7704,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7685,7 +7747,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7695,14 +7757,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45692</v>
+        <v>44673</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7715,7 +7777,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7758,7 +7820,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7772,10 +7834,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44951</v>
+        <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7787,13 +7849,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7836,7 +7893,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7846,14 +7903,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44924</v>
+        <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7865,13 +7922,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7914,7 +7966,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7928,10 +7980,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44583</v>
+        <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7943,13 +7995,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7992,7 +8039,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8006,10 +8053,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8022,7 +8069,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8065,7 +8112,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8079,10 +8126,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45387</v>
+        <v>44905</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8094,8 +8141,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>13.7</v>
+        <v>4.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8138,7 +8190,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8152,10 +8204,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46216</v>
+        <v>45719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8168,7 +8220,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8211,7 +8263,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8225,10 +8277,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45629</v>
+        <v>44673</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8241,7 +8293,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8284,7 +8336,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8298,10 +8350,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44905</v>
+        <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8313,13 +8365,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.7</v>
+        <v>13.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8362,7 +8409,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8376,10 +8423,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46216</v>
+        <v>44915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8392,7 +8439,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8435,7 +8482,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8449,10 +8496,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46216</v>
+        <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8464,8 +8511,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8508,7 +8560,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8522,10 +8574,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44851</v>
+        <v>44951</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8537,8 +8589,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8581,7 +8638,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8595,10 +8652,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46216</v>
+        <v>45082</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8611,7 +8668,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>0.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8654,7 +8711,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8664,14 +8721,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44673</v>
+        <v>44677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8684,7 +8741,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8727,7 +8784,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8741,10 +8798,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44677</v>
+        <v>44937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8757,7 +8814,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8800,7 +8857,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8814,10 +8871,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44952</v>
+        <v>44937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8829,13 +8886,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8878,7 +8930,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8892,10 +8944,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44920</v>
+        <v>45692</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8908,7 +8960,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>11.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8951,7 +9003,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8961,14 +9013,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45811</v>
+        <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8981,7 +9033,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9024,7 +9076,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9038,10 +9090,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45842</v>
+        <v>45166</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9053,13 +9105,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9102,7 +9149,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9116,10 +9163,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45861</v>
+        <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9131,13 +9178,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>10.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9180,24 +9222,24 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 104-2024</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45302</v>
+        <v>45155</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9210,7 +9252,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9253,148 +9295,221 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
+          <t>S 104-2024</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>S 156-2024</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D104" s="1" t="n">
+      <c r="D105" s="1" t="n">
         <v>45309</v>
       </c>
-      <c r="E104" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
+      <c r="E105" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
         <v>7.2</v>
       </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>S 2021-2026</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D105" s="1" t="n">
+      <c r="D106" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="E105" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
+      <c r="E106" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
         <v>2.6</v>
       </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="2" t="inlineStr"/>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44775</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44952</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>46007</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45618</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>44775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45499</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44851</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>46049</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>44673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44917</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>46087</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>45848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44678</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45842</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45387</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44915</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45861</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44920</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>46182</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>46203</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44583</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45628</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>46210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44673</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44905</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>44673</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44951</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45082</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45692</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45166</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>45155</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45302</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>46210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44775</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44952</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>46007</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45618</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>44775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45499</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45834</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44851</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>46049</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>44673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44917</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>46087</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>45848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44678</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45842</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45387</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44915</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45861</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44920</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>46182</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>46203</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44583</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45628</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>46210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44673</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44905</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>44673</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44951</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45082</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45692</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45166</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>45155</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45302</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>46210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE106"/>
+  <dimension ref="A1:AE107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1708,11 +1708,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1721,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1733,21 +1738,133 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1755,153 +1872,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 62578-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45817</v>
+        <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2074,164 +2074,164 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 61363-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45618</v>
+        <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,17 +2375,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2408,159 +2408,159 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2924,8 +2924,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2934,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2952,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -2961,158 +2966,153 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44915</v>
+        <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3154,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3166,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46008</v>
+        <v>44915</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,20 +3247,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3283,46 +3283,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3339,7 +3339,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3392,42 +3392,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,17 +3457,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3497,35 +3497,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44851</v>
+        <v>44915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5010,13 +5010,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5059,7 +5054,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5073,10 +5068,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46049</v>
+        <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5084,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5132,7 +5127,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5146,10 +5141,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45476</v>
+        <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5161,13 +5156,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5210,7 +5200,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5224,10 +5214,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45447</v>
+        <v>44951</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5241,11 +5231,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5288,7 +5278,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5298,14 +5288,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44673</v>
+        <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5318,7 +5308,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5361,7 +5351,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5375,10 +5365,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44917</v>
+        <v>45811</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5391,7 +5381,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5434,7 +5424,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5448,10 +5438,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46087</v>
+        <v>45842</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5469,7 +5459,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5512,7 +5502,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5522,14 +5512,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45756</v>
+        <v>45953</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5541,13 +5531,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5590,7 +5575,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5600,14 +5585,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45953</v>
+        <v>45756</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5619,8 +5604,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5663,7 +5653,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5677,10 +5667,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44952</v>
+        <v>45861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5694,11 +5684,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5741,7 +5731,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5755,10 +5745,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45811</v>
+        <v>44915</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5771,7 +5761,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5814,7 +5804,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5828,10 +5818,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45783</v>
+        <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5844,7 +5834,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5887,7 +5877,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5901,10 +5891,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44924</v>
+        <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5916,13 +5906,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5965,7 +5950,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5979,10 +5964,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45995</v>
+        <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5980,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6038,7 +6023,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6052,10 +6037,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45043</v>
+        <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6067,8 +6052,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6111,7 +6101,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6125,10 +6115,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45848</v>
+        <v>46049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6141,7 +6131,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6184,7 +6174,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6198,10 +6188,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45450</v>
+        <v>45476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6209,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6262,7 +6252,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6276,10 +6266,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44678</v>
+        <v>45397</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6282,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>13.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6335,7 +6325,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6349,10 +6339,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44565</v>
+        <v>46087</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6370,7 +6360,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6413,7 +6403,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6427,10 +6417,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45842</v>
+        <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6442,13 +6432,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6491,7 +6476,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6501,14 +6486,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45518</v>
+        <v>44673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,7 +6506,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6564,7 +6549,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6578,10 +6563,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45842</v>
+        <v>44565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6599,7 +6584,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6642,7 +6627,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6652,14 +6637,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46161</v>
+        <v>45848</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6672,7 +6657,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6715,7 +6700,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6729,10 +6714,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45387</v>
+        <v>45995</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6745,7 +6730,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>13.7</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6788,7 +6773,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6802,10 +6787,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44915</v>
+        <v>45783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6818,7 +6803,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6846,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6860,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45716</v>
+        <v>44966</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6891,7 +6876,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6919,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,10 +6933,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45861</v>
+        <v>45043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6963,13 +6948,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7012,7 +6992,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7022,14 +7002,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44920</v>
+        <v>45628</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7042,7 +7022,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7085,7 +7065,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7095,14 +7075,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46182</v>
+        <v>45450</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7114,8 +7094,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7158,7 +7143,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7172,10 +7157,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44966</v>
+        <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7188,7 +7173,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7231,7 +7216,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7245,10 +7230,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45113</v>
+        <v>45842</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7260,8 +7245,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7304,7 +7294,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7318,10 +7308,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45629</v>
+        <v>45300</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7334,7 +7324,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>10.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7377,7 +7367,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7391,10 +7381,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45629</v>
+        <v>45113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7407,7 +7397,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7450,7 +7440,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7460,14 +7450,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46203</v>
+        <v>46161</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7480,7 +7470,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>13.8</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7523,7 +7513,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7537,10 +7527,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44583</v>
+        <v>45716</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7552,13 +7542,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7601,7 +7586,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7611,14 +7596,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45628</v>
+        <v>45719</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7631,7 +7616,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7674,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7684,14 +7669,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46210</v>
+        <v>46182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7704,7 +7689,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7747,7 +7732,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7757,14 +7742,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44673</v>
+        <v>45082</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7777,7 +7762,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7820,7 +7805,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7834,10 +7819,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46216</v>
+        <v>45476</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7849,8 +7834,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7893,7 +7883,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7907,10 +7897,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46216</v>
+        <v>45629</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7923,7 +7913,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7966,7 +7956,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7980,10 +7970,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46216</v>
+        <v>45692</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7996,7 +7986,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>11.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8039,7 +8029,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8053,10 +8043,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46216</v>
+        <v>44951</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8068,8 +8058,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8112,7 +8107,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8122,14 +8117,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44905</v>
+        <v>44924</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8143,11 +8138,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8190,7 +8185,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8204,10 +8199,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45719</v>
+        <v>44583</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8219,8 +8214,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8263,7 +8263,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8277,10 +8277,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44673</v>
+        <v>46203</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>13.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8336,7 +8336,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45397</v>
+        <v>45387</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44915</v>
+        <v>46210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8482,7 +8482,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8496,10 +8496,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44951</v>
+        <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8511,13 +8511,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8560,7 +8555,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8574,10 +8569,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44951</v>
+        <v>44905</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8595,7 +8590,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8638,7 +8633,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8652,10 +8647,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45082</v>
+        <v>44851</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8668,7 +8663,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8711,7 +8706,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8725,10 +8720,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44677</v>
+        <v>46216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8741,7 +8736,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8784,7 +8779,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8798,10 +8793,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44937</v>
+        <v>46216</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8814,7 +8809,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8857,7 +8852,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8867,14 +8862,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44937</v>
+        <v>44673</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8887,7 +8882,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8930,7 +8925,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8944,10 +8939,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45692</v>
+        <v>46216</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8960,7 +8955,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9003,7 +8998,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9013,14 +9008,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44935</v>
+        <v>46216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9033,7 +9028,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9076,7 +9071,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9090,10 +9085,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45166</v>
+        <v>44677</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9106,7 +9101,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9149,7 +9144,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9163,10 +9158,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45300</v>
+        <v>44952</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9178,8 +9173,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>10.1</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45155</v>
+        <v>44920</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9295,24 +9295,24 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S 104-2024</t>
+          <t>A 40142-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45302</v>
+        <v>46293</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9368,148 +9368,221 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
+          <t>S 104-2024</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>S 156-2024</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D105" s="1" t="n">
+      <c r="D106" s="1" t="n">
         <v>45309</v>
       </c>
-      <c r="E105" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
+      <c r="E106" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
         <v>7.2</v>
       </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>S 2021-2026</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D106" s="1" t="n">
+      <c r="D107" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="E106" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
+      <c r="E107" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
         <v>2.6</v>
       </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" s="2" t="inlineStr"/>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 3914-2023</t>
+          <t>A 31523-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44952</v>
+        <v>44775</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1708,16 +1708,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1726,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1738,21 +1733,138 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1760,148 +1872,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62578-2025</t>
+          <t>A 27948-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46007</v>
+        <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2074,164 +2074,164 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Mindre märgborre
 Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61363-2022</t>
+          <t>A 54703-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44915</v>
+        <v>45618</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,17 +2375,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2408,159 +2408,159 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 31575-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45499</v>
+        <v>44775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2924,13 +2924,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2939,10 +2934,10 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2957,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -2966,153 +2961,158 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 30949-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,20 +3142,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3166,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44915</v>
+        <v>45834</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3283,39 +3283,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44915</v>
+        <v>44851</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5010,8 +5010,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5054,7 +5059,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5068,10 +5073,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44937</v>
+        <v>45811</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5084,7 +5089,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5127,7 +5132,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5141,10 +5146,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45155</v>
+        <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5156,8 +5161,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5200,7 +5210,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5214,10 +5224,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44951</v>
+        <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5231,11 +5241,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5278,7 +5288,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5288,14 +5298,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45518</v>
+        <v>44673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5308,7 +5318,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5351,7 +5361,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5365,10 +5375,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45811</v>
+        <v>45842</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5380,8 +5390,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5424,7 +5439,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5438,10 +5453,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45842</v>
+        <v>44917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5453,13 +5468,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5502,7 +5512,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5512,14 +5522,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45953</v>
+        <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5531,8 +5541,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5575,7 +5590,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5589,10 +5604,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45756</v>
+        <v>45861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5610,7 +5625,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5653,7 +5668,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5667,10 +5682,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45861</v>
+        <v>46049</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5682,13 +5697,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5731,7 +5741,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5741,14 +5751,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44915</v>
+        <v>45953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5761,7 +5771,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5804,7 +5814,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5818,10 +5828,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44673</v>
+        <v>44952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5833,8 +5843,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5877,7 +5892,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5891,10 +5906,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44935</v>
+        <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5906,8 +5921,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5950,7 +5970,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5964,10 +5984,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44917</v>
+        <v>46087</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5979,8 +5999,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6023,7 +6048,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6037,10 +6062,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6058,7 +6083,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6101,7 +6126,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6111,14 +6136,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46049</v>
+        <v>45518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6131,7 +6156,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6174,7 +6199,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6188,10 +6213,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45476</v>
+        <v>45783</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6203,13 +6228,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6252,7 +6272,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6266,10 +6286,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45397</v>
+        <v>45387</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6282,7 +6302,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6325,7 +6345,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6339,10 +6359,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46087</v>
+        <v>44915</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6354,13 +6374,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6403,7 +6418,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6417,10 +6432,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45166</v>
+        <v>44920</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6433,7 +6448,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6476,7 +6491,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6490,10 +6505,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44673</v>
+        <v>45995</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6506,7 +6521,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6549,7 +6564,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6563,10 +6578,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44565</v>
+        <v>45043</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6578,13 +6593,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6644,7 +6654,7 @@
         <v>45848</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6700,7 +6710,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6714,10 +6724,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45995</v>
+        <v>44966</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6730,7 +6740,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6773,7 +6783,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6787,10 +6797,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45783</v>
+        <v>45450</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6802,8 +6812,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6846,7 +6861,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6860,10 +6875,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44966</v>
+        <v>45113</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6876,7 +6891,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6919,7 +6934,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6933,10 +6948,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45043</v>
+        <v>44678</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6949,7 +6964,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6992,7 +7007,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7002,14 +7017,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7022,7 +7037,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7065,7 +7080,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7079,10 +7094,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45450</v>
+        <v>45629</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7094,13 +7109,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7143,7 +7153,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7157,10 +7167,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44678</v>
+        <v>45842</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7172,8 +7182,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7216,7 +7231,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7230,10 +7245,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45842</v>
+        <v>44583</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7251,7 +7266,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7294,7 +7309,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7304,14 +7319,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45300</v>
+        <v>45628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7324,7 +7339,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7367,7 +7382,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7377,14 +7392,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45113</v>
+        <v>46161</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7397,7 +7412,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7440,7 +7455,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7454,10 +7469,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46161</v>
+        <v>44673</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7470,7 +7485,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7530,7 +7545,7 @@
         <v>45716</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7586,7 +7601,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7600,10 +7615,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45719</v>
+        <v>44905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7615,8 +7630,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7659,7 +7679,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7669,14 +7689,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46182</v>
+        <v>45719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7689,7 +7709,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7732,7 +7752,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7742,14 +7762,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45082</v>
+        <v>46182</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7762,7 +7782,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7805,7 +7825,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7819,10 +7839,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45476</v>
+        <v>44673</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7834,13 +7854,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7883,7 +7898,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7897,10 +7912,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45629</v>
+        <v>45397</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7913,7 +7928,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7956,7 +7971,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7970,10 +7985,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45692</v>
+        <v>44915</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7986,7 +8001,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11.2</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8029,7 +8044,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8043,10 +8058,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44951</v>
+        <v>46203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8058,13 +8073,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.7</v>
+        <v>13.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8107,7 +8117,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8117,14 +8127,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44924</v>
+        <v>44951</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8138,11 +8148,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8185,7 +8195,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8199,10 +8209,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44583</v>
+        <v>44951</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8216,11 +8226,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8263,7 +8273,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8277,10 +8287,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8293,7 +8303,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>13.8</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8336,7 +8346,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8350,10 +8360,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45387</v>
+        <v>45082</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8366,7 +8376,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>13.7</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8409,7 +8419,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8423,10 +8433,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8439,7 +8449,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8482,7 +8492,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8496,10 +8506,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45629</v>
+        <v>44677</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8512,7 +8522,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8555,7 +8565,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8569,10 +8579,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44905</v>
+        <v>46216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8584,13 +8594,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8633,7 +8638,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8647,10 +8652,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44851</v>
+        <v>46216</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8663,7 +8668,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8723,7 +8728,7 @@
         <v>46216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8779,7 +8784,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8793,10 +8798,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46216</v>
+        <v>44937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8809,7 +8814,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8852,7 +8857,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8862,14 +8867,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44673</v>
+        <v>44937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8882,7 +8887,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8925,7 +8930,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8939,10 +8944,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46216</v>
+        <v>45692</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8955,7 +8960,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8998,7 +9003,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9008,14 +9013,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46216</v>
+        <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9028,7 +9033,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9071,7 +9076,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9085,10 +9090,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44677</v>
+        <v>45166</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9101,7 +9106,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9144,7 +9149,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9158,10 +9163,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44952</v>
+        <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9173,13 +9178,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44920</v>
+        <v>45155</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
         <v>46293</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>46210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 37244-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44775</v>
+        <v>45540</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1709,19 +1709,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1745,9 +1745,121 @@
         <v>5</v>
       </c>
       <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Talltita
+Vedskivlav
+Grovticka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1755,116 +1867,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 3914-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>44952</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>15.3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1872,155 +1984,43 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 37244-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Talltita
-Vedskivlav
-Grovticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 54703-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45817</v>
+        <v>45618</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2062,505 +2062,505 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 12620-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 62578-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>46007</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>3.4</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Mindre märgborre
 Vedticka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 12620-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43308-2024</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45568</v>
+        <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2859,253 +2859,253 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 43308-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Dropptaggsvamp
 Tallticka</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45834</v>
+        <v>44523</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,8 +3246,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3256,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3271,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3283,46 +3288,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3336,10 +3345,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46008</v>
+        <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,13 +3361,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3392,42 +3401,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3444,7 +3453,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,16 +3466,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3481,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3497,42 +3506,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3546,10 +3555,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44523</v>
+        <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,16 +3570,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3603,43 +3607,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15131-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44658</v>
+        <v>44569</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4124,8 +4124,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4168,7 +4173,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19934-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4182,10 +4187,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44697</v>
+        <v>44569</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4197,8 +4202,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4241,7 +4251,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19944-2022</t>
+          <t>A 15131-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4255,10 +4265,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44697</v>
+        <v>44658</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4271,7 +4281,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4314,7 +4324,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 28405-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4328,10 +4338,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44569</v>
+        <v>44747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4343,13 +4353,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4392,7 +4397,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 17173-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4406,10 +4411,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44569</v>
+        <v>44677</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4421,13 +4426,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28405-2022</t>
+          <t>A 28964-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44747</v>
+        <v>44749</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17173-2022</t>
+          <t>A 19934-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44677</v>
+        <v>44697</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10082-2022</t>
+          <t>A 19944-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44621</v>
+        <v>44697</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28964-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44749</v>
+        <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18091-2022</t>
+          <t>A 10082-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44684</v>
+        <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 18091-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44747</v>
+        <v>44684</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4908,7 +4908,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44851</v>
+        <v>44915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>45628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5010,13 +5010,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5059,7 +5054,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5073,10 +5068,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45811</v>
+        <v>44673</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5084,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5132,7 +5127,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5146,10 +5141,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45476</v>
+        <v>44677</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5161,13 +5156,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5210,7 +5200,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5220,14 +5210,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45447</v>
+        <v>44935</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5239,13 +5229,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5288,7 +5273,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5302,10 +5287,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44673</v>
+        <v>44917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5318,7 +5303,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5361,7 +5346,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5375,10 +5360,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45842</v>
+        <v>44952</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5392,11 +5377,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5439,7 +5424,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5453,10 +5438,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44917</v>
+        <v>45447</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5468,8 +5453,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5512,7 +5502,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5526,10 +5516,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45756</v>
+        <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5541,13 +5531,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5590,7 +5575,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5604,10 +5589,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45861</v>
+        <v>44937</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5619,13 +5604,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5668,7 +5648,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5682,10 +5662,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46049</v>
+        <v>45300</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5698,7 +5678,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>10.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5741,7 +5721,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5751,14 +5731,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45953</v>
+        <v>44920</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5771,7 +5751,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5814,7 +5794,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5828,10 +5808,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44952</v>
+        <v>45155</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5843,13 +5823,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5892,7 +5867,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5902,14 +5877,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44924</v>
+        <v>45476</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,7 +5902,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5970,7 +5945,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5984,10 +5959,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46087</v>
+        <v>45113</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5999,13 +5974,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6048,7 +6018,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6062,10 +6032,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44565</v>
+        <v>44951</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6079,11 +6049,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6126,7 +6096,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6136,14 +6106,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45518</v>
+        <v>45719</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6126,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6199,7 +6169,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6213,10 +6183,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45783</v>
+        <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6199,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6272,7 +6242,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6282,14 +6252,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45387</v>
+        <v>45518</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6302,7 +6272,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13.7</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6345,7 +6315,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6359,10 +6329,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44915</v>
+        <v>45166</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6375,7 +6345,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6418,7 +6388,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6432,10 +6402,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44920</v>
+        <v>45082</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6448,7 +6418,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6491,7 +6461,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6505,10 +6475,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45995</v>
+        <v>44673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6521,7 +6491,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6564,7 +6534,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6578,10 +6548,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45043</v>
+        <v>44565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6593,8 +6563,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6637,7 +6612,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6651,10 +6626,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45848</v>
+        <v>45476</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6666,8 +6641,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6710,7 +6690,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6724,10 +6704,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44966</v>
+        <v>45629</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6740,7 +6720,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6783,7 +6763,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6797,10 +6777,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45450</v>
+        <v>45692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6812,13 +6792,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.7</v>
+        <v>11.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6861,7 +6836,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6875,10 +6850,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45113</v>
+        <v>44951</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6890,8 +6865,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6934,7 +6914,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6944,14 +6924,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44678</v>
+        <v>44924</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6963,8 +6943,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7007,7 +6992,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7021,10 +7006,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45629</v>
+        <v>44583</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7036,8 +7021,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7080,7 +7070,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7094,10 +7084,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45629</v>
+        <v>45811</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7110,7 +7100,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7153,7 +7143,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7167,10 +7157,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45842</v>
+        <v>45387</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7182,13 +7172,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.7</v>
+        <v>13.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7231,7 +7216,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7245,10 +7230,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44583</v>
+        <v>45629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7260,13 +7245,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7309,7 +7289,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7319,14 +7299,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45628</v>
+        <v>44905</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7338,8 +7318,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7382,7 +7367,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7392,14 +7377,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46161</v>
+        <v>44851</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7412,7 +7397,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7472,7 +7457,7 @@
         <v>44673</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7528,7 +7513,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7542,10 +7527,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45716</v>
+        <v>44966</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7558,7 +7543,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7601,7 +7586,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7615,10 +7600,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44905</v>
+        <v>45842</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7632,11 +7617,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7679,7 +7664,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7693,10 +7678,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45719</v>
+        <v>45861</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7708,8 +7693,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7752,7 +7742,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7762,14 +7752,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46182</v>
+        <v>45756</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7781,8 +7771,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7825,7 +7820,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7839,10 +7834,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44673</v>
+        <v>44915</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7855,7 +7850,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7898,7 +7893,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7908,14 +7903,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45397</v>
+        <v>45953</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7928,7 +7923,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.6</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7971,7 +7966,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7985,10 +7980,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44915</v>
+        <v>46049</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8001,7 +7996,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8044,7 +8039,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8058,10 +8053,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46203</v>
+        <v>46087</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8073,8 +8068,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>13.8</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8117,7 +8117,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44951</v>
+        <v>45848</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8146,13 +8146,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8195,7 +8190,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8209,10 +8204,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44951</v>
+        <v>45995</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8224,13 +8219,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8273,7 +8263,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8287,10 +8277,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46210</v>
+        <v>45783</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8303,7 +8293,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8346,7 +8336,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8360,10 +8350,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45082</v>
+        <v>45043</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8376,7 +8366,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8419,7 +8409,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8433,10 +8423,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46216</v>
+        <v>45450</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8448,8 +8438,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8492,7 +8487,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8506,10 +8501,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8522,7 +8517,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8565,7 +8560,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8579,10 +8574,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46216</v>
+        <v>45842</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8594,8 +8589,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8638,7 +8638,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8648,14 +8648,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46216</v>
+        <v>46161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8711,7 +8711,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46216</v>
+        <v>45716</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8784,7 +8784,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8794,14 +8794,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44937</v>
+        <v>46182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8857,7 +8857,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44937</v>
+        <v>46203</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>13.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8930,7 +8930,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45692</v>
+        <v>46210</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9003,7 +9003,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9013,14 +9013,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44935</v>
+        <v>46216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9076,7 +9076,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9090,10 +9090,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45166</v>
+        <v>46216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45300</v>
+        <v>46216</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>10.1</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45155</v>
+        <v>46216</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
         <v>46293</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>46210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 37244-2024</t>
+          <t>A 31523-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45540</v>
+        <v>44775</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1709,19 +1709,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1745,9 +1745,238 @@
         <v>5</v>
       </c>
       <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 37244-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45540</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Talltita
@@ -1755,272 +1984,43 @@
 Grovticka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 27948-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45618</v>
+        <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2074,493 +2074,493 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 12620-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 12620-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="D18" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 43308-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45499</v>
+        <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2825,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2859,253 +2859,253 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Dropptaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 30949-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 43308-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45568</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44523</v>
+        <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,22 +3246,17 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3276,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3288,43 +3283,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
@@ -3348,7 +3339,7 @@
         <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3436,7 +3427,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3453,7 +3444,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,17 +3457,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3490,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3506,42 +3497,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3555,10 +3546,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46008</v>
+        <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3570,11 +3561,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3607,39 +3603,43 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 15131-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44569</v>
+        <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4124,13 +4124,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4173,7 +4168,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 19934-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4187,10 +4182,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44569</v>
+        <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4202,13 +4197,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4251,7 +4241,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15131-2022</t>
+          <t>A 19944-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4265,10 +4255,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44658</v>
+        <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4281,7 +4271,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4324,7 +4314,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28405-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4338,10 +4328,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44747</v>
+        <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4353,8 +4343,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4397,7 +4392,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17173-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4411,10 +4406,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44677</v>
+        <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4426,8 +4421,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28964-2022</t>
+          <t>A 28405-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44749</v>
+        <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19934-2022</t>
+          <t>A 17173-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44697</v>
+        <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19944-2022</t>
+          <t>A 10082-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44697</v>
+        <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 28964-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44747</v>
+        <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10082-2022</t>
+          <t>A 18091-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44621</v>
+        <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18091-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44684</v>
+        <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4908,7 +4908,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44915</v>
+        <v>44851</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45628</v>
+        <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5010,8 +5010,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5054,7 +5059,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5068,10 +5073,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44673</v>
+        <v>46049</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5084,7 +5089,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5127,7 +5132,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5141,10 +5146,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44677</v>
+        <v>45476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5156,8 +5161,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5200,7 +5210,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5210,14 +5220,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44935</v>
+        <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5229,8 +5239,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5273,7 +5288,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5287,10 +5302,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44917</v>
+        <v>44673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5303,7 +5318,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5346,7 +5361,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5360,10 +5375,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44952</v>
+        <v>46087</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5377,11 +5392,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5424,7 +5439,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5438,10 +5453,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45447</v>
+        <v>44917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5453,13 +5468,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5502,7 +5512,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5512,14 +5522,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44937</v>
+        <v>45953</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5532,7 +5542,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5575,7 +5585,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5589,10 +5599,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44937</v>
+        <v>45756</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5604,8 +5614,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5648,7 +5663,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5662,10 +5677,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45300</v>
+        <v>45811</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5678,7 +5693,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5721,7 +5736,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5735,10 +5750,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44920</v>
+        <v>44952</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5750,8 +5765,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5794,7 +5814,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5808,10 +5828,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45155</v>
+        <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5824,7 +5844,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5867,7 +5887,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5877,14 +5897,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45476</v>
+        <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5902,7 +5922,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5945,7 +5965,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5959,10 +5979,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45113</v>
+        <v>45995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5975,7 +5995,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6018,7 +6038,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6032,10 +6052,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44951</v>
+        <v>45043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6047,13 +6067,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6096,7 +6111,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6110,10 +6125,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45719</v>
+        <v>45842</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6125,8 +6140,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6169,7 +6189,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6183,10 +6203,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45397</v>
+        <v>45848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6199,7 +6219,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>13.6</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6242,7 +6262,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6252,14 +6272,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45518</v>
+        <v>45861</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6271,8 +6291,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6315,7 +6340,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6329,10 +6354,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45166</v>
+        <v>45450</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6344,8 +6369,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6388,7 +6418,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6402,10 +6432,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45082</v>
+        <v>44565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6417,8 +6447,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6461,7 +6496,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6475,10 +6510,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44673</v>
+        <v>44678</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6491,7 +6526,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6534,7 +6569,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6548,10 +6583,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44565</v>
+        <v>45842</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6569,7 +6604,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6612,7 +6647,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6622,14 +6657,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45476</v>
+        <v>45518</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6641,13 +6676,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6690,7 +6720,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6704,10 +6734,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45629</v>
+        <v>45387</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6720,7 +6750,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>13.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6763,7 +6793,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6777,10 +6807,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45692</v>
+        <v>44915</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6793,7 +6823,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>11.2</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6836,7 +6866,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6846,14 +6876,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44951</v>
+        <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6865,13 +6895,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6914,7 +6939,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,14 +6949,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44924</v>
+        <v>44920</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6943,13 +6968,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6992,7 +7012,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7006,10 +7026,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44583</v>
+        <v>45716</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7021,13 +7041,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7070,7 +7085,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7084,10 +7099,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45811</v>
+        <v>44966</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7115,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7143,7 +7158,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7157,10 +7172,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45387</v>
+        <v>45113</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7188,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>13.7</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7216,7 +7231,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7233,7 +7248,7 @@
         <v>45629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7261,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7289,7 +7304,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7303,10 +7318,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44905</v>
+        <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7318,13 +7333,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7367,7 +7377,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7377,14 +7387,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44851</v>
+        <v>46182</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7397,7 +7407,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7440,7 +7450,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7450,14 +7460,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44673</v>
+        <v>44583</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7469,8 +7479,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7513,7 +7528,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7523,14 +7538,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44966</v>
+        <v>45628</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7543,7 +7558,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7586,7 +7601,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7596,14 +7611,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45842</v>
+        <v>44673</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7615,13 +7630,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7664,7 +7674,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7678,10 +7688,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45861</v>
+        <v>46203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7693,13 +7703,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>8</v>
+        <v>13.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7742,7 +7747,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7756,10 +7761,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45756</v>
+        <v>46210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7771,13 +7776,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44915</v>
+        <v>44905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7849,8 +7849,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7893,7 +7898,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7903,14 +7908,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45953</v>
+        <v>45719</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7923,7 +7928,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7966,7 +7971,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7980,10 +7985,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46049</v>
+        <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7996,7 +8001,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8039,7 +8044,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8053,10 +8058,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46087</v>
+        <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8068,13 +8073,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8117,7 +8117,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45848</v>
+        <v>46216</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8190,7 +8190,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45995</v>
+        <v>46216</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8263,7 +8263,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8277,10 +8277,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45783</v>
+        <v>44673</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8336,7 +8336,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45043</v>
+        <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45450</v>
+        <v>44915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8438,13 +8438,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8487,7 +8482,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8501,10 +8496,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44678</v>
+        <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8516,8 +8511,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8560,7 +8560,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45842</v>
+        <v>44951</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8591,11 +8591,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8638,7 +8638,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8648,14 +8648,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46161</v>
+        <v>45082</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8711,7 +8711,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45716</v>
+        <v>44677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8784,7 +8784,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8794,14 +8794,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46182</v>
+        <v>44937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8857,7 +8857,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46203</v>
+        <v>44937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>13.8</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8930,7 +8930,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 40142-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46210</v>
+        <v>46293</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9003,7 +9003,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46216</v>
+        <v>45692</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9076,7 +9076,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9086,14 +9086,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46216</v>
+        <v>44935</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46216</v>
+        <v>45166</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46216</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9295,7 +9295,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40142-2026</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46293</v>
+        <v>45155</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9385,7 +9385,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>46210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3919-2023</t>
+          <t>A 31459-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44952</v>
+        <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -754,25 +754,20 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -787,18 +782,145 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
       </c>
       <c r="T3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Sårläka
+Tallticka
+Talltita
+Ullticka
+Älg
+Björksplintborre
+Mörk husmossa
+Thomsons trägnagare
+Tibast
+Blåsippa
+Spillkråka
+Sångsvan
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 3919-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
         <v>62</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>61</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Stare
@@ -816,158 +938,36 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 31459-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U4" t="n">
-        <v>9</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Sårläka
-Tallticka
-Talltita
-Ullticka
-Älg
-Björksplintborre
-Mörk husmossa
-Thomsons trägnagare
-Tibast
-Blåsippa
-Spillkråka
-Sångsvan
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1708,11 +1708,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1721,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1733,21 +1738,133 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1755,153 +1872,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 62578-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45817</v>
+        <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2074,164 +2074,164 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 61363-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45618</v>
+        <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,17 +2375,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2408,159 +2408,159 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2924,8 +2924,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2934,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2952,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -2961,151 +2966,146 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44851</v>
+        <v>44915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5010,13 +5010,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5059,7 +5054,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5073,10 +5068,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46049</v>
+        <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5084,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5132,7 +5127,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5146,10 +5141,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45476</v>
+        <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5161,13 +5156,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5210,7 +5200,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5224,10 +5214,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45447</v>
+        <v>44951</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5241,11 +5231,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5288,7 +5278,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5298,14 +5288,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44673</v>
+        <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5318,7 +5308,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5361,7 +5351,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5375,10 +5365,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46087</v>
+        <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5390,13 +5380,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5439,7 +5424,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5453,10 +5438,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44917</v>
+        <v>45756</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5468,8 +5453,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5512,7 +5502,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5522,14 +5512,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45953</v>
+        <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5542,7 +5532,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5585,7 +5575,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5595,14 +5585,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45756</v>
+        <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5614,13 +5604,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5680,7 +5665,7 @@
         <v>45811</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5736,7 +5721,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5750,10 +5735,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44952</v>
+        <v>46087</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5767,11 +5752,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5814,7 +5799,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5828,10 +5813,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45783</v>
+        <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5844,7 +5829,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5887,7 +5872,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5901,10 +5886,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44924</v>
+        <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5916,13 +5901,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5965,7 +5945,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5979,10 +5959,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45995</v>
+        <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5975,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6038,7 +6018,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6052,10 +6032,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45043</v>
+        <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6067,8 +6047,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6111,7 +6096,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6125,10 +6110,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45842</v>
+        <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6131,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6189,7 +6174,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6203,10 +6188,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45848</v>
+        <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6204,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>13.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6262,7 +6247,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6276,10 +6261,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45861</v>
+        <v>45842</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,7 +6282,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6340,7 +6325,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6354,10 +6339,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45450</v>
+        <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6369,13 +6354,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6418,7 +6398,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6432,10 +6412,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44565</v>
+        <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6447,13 +6427,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6496,7 +6471,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6510,10 +6485,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44678</v>
+        <v>45783</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6526,7 +6501,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6569,7 +6544,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6583,10 +6558,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45842</v>
+        <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6598,13 +6573,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6647,7 +6617,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6657,14 +6627,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45518</v>
+        <v>45043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6677,7 +6647,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6720,7 +6690,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6734,10 +6704,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45387</v>
+        <v>44673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6750,7 +6720,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>13.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6793,7 +6763,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6807,10 +6777,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44915</v>
+        <v>45861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6822,8 +6792,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6866,7 +6841,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6876,14 +6851,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46161</v>
+        <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6895,8 +6870,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6939,7 +6919,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6953,10 +6933,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44920</v>
+        <v>45450</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6968,8 +6948,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7012,7 +6997,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7026,10 +7011,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45716</v>
+        <v>44678</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7042,7 +7027,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7085,7 +7070,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7099,10 +7084,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44966</v>
+        <v>45842</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7114,8 +7099,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7158,7 +7148,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7172,10 +7162,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45113</v>
+        <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7188,7 +7178,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7231,7 +7221,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7241,14 +7231,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45629</v>
+        <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7261,7 +7251,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7304,7 +7294,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7318,10 +7308,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45629</v>
+        <v>45716</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7334,7 +7324,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7377,7 +7367,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7387,14 +7377,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46182</v>
+        <v>45628</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7407,7 +7397,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7450,7 +7440,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7460,14 +7450,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44583</v>
+        <v>46182</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7479,13 +7469,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7528,7 +7513,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7538,14 +7523,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45628</v>
+        <v>45300</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7558,7 +7543,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7601,7 +7586,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7611,14 +7596,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44673</v>
+        <v>46203</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7631,7 +7616,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>13.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7674,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7688,10 +7673,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46203</v>
+        <v>45113</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7704,7 +7689,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>13.8</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7764,7 +7749,7 @@
         <v>46210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7820,7 +7805,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7834,10 +7819,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44905</v>
+        <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7849,13 +7834,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7898,7 +7878,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7912,10 +7892,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45719</v>
+        <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7928,7 +7908,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7988,7 +7968,7 @@
         <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8061,7 +8041,7 @@
         <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8117,7 +8097,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8131,10 +8111,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46216</v>
+        <v>45719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8147,7 +8127,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8190,7 +8170,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8204,10 +8184,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46216</v>
+        <v>45082</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8220,7 +8200,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8263,7 +8243,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8277,10 +8257,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44673</v>
+        <v>45476</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8292,8 +8272,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8336,7 +8321,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8350,10 +8335,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45397</v>
+        <v>45629</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8366,7 +8351,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>13.6</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8409,7 +8394,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8423,10 +8408,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44915</v>
+        <v>45692</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8439,7 +8424,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>11.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8499,7 +8484,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8560,7 +8545,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8570,14 +8555,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44951</v>
+        <v>44924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8591,11 +8576,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8638,7 +8623,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8652,10 +8637,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45082</v>
+        <v>44583</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8667,8 +8652,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8711,7 +8701,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8725,10 +8715,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44677</v>
+        <v>45387</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8741,7 +8731,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.9</v>
+        <v>13.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8784,7 +8774,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 40142-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8798,10 +8788,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44937</v>
+        <v>46293</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8814,7 +8804,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8857,7 +8847,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8871,10 +8861,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44937</v>
+        <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8887,7 +8877,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8930,7 +8920,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40142-2026</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8944,10 +8934,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46293</v>
+        <v>44905</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8959,8 +8949,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9003,7 +8998,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9017,10 +9012,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45692</v>
+        <v>44851</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9033,7 +9028,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>11.2</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9076,7 +9071,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9090,10 +9085,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44935</v>
+        <v>44673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9106,7 +9101,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9149,7 +9144,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9163,10 +9158,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45166</v>
+        <v>44677</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9179,7 +9174,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9222,7 +9217,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9236,10 +9231,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>44952</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9251,8 +9246,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>10.1</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9295,7 +9295,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45155</v>
+        <v>44920</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9385,7 +9385,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>46210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45817</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45618</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45499</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44951</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45756</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45811</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>46087</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45842</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45783</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>44673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45450</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44678</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45842</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45716</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45628</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>46182</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45300</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>46203</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45113</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45082</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45476</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45629</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45692</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44583</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45387</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>46293</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44905</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44851</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44677</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44952</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44920</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>46210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44474</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45540</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45817</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45618</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>44498</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45499</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>44915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44523</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44697</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44569</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44621</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44951</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45756</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45811</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>46087</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45842</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45783</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>44673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45450</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44678</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45842</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45716</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45628</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>46182</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45300</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>46203</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45113</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>46216</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46216</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>46216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45082</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45476</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45629</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45692</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44583</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45387</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>46293</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45629</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44905</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44851</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44677</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44952</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44920</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>46210</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE107"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31459-2025</t>
+          <t>A 3919-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45833</v>
+        <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -754,20 +754,25 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -782,18 +787,140 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
       </c>
       <c r="T3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U3" t="n">
+        <v>61</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Stare
+Brunlångöra
+Grönsångare
+Nordfladdermus
+Tallticka
+Tofsmes
+Dvärgpipistrell
+Grönsiska
+Kråka
+Kungsfågel
+Större brunfladdermus
+Svartvit flugsnappare
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 31459-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
         <v>17</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>9</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Sårläka
@@ -811,163 +938,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 3919-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>62</v>
-      </c>
-      <c r="U4" t="n">
-        <v>61</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Stare
-Brunlångöra
-Grönsångare
-Nordfladdermus
-Tallticka
-Tofsmes
-Dvärgpipistrell
-Grönsiska
-Kråka
-Kungsfågel
-Större brunfladdermus
-Svartvit flugsnappare
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1338,24 +1338,24 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S 7486-2021</t>
+          <t>A 22172-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44474</v>
+        <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,22 +1367,17 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>11.3</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1397,132 +1392,21 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ekticka
-Lunglav
-Oxtungssvamp
-Veckticka
-Hasselticka
-Stubbspretmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 7486-2021 artfynd.xlsx", "S 7486-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 7486-2021 karta.png", "S 7486-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 7486-2021 georefererad karta.tif", "S 7486-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 7486-2021 FSC-klagomål.docx", "S 7486-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 7486-2021 FSC-klagomål mail.docx", "S 7486-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 7486-2021 tillsynsbegäran.docx", "S 7486-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 7486-2021 tillsynsbegäran mail.docx", "S 7486-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 22172-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44712</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>76</v>
-      </c>
-      <c r="U9" t="n">
-        <v>76</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Gullpudra
@@ -1532,112 +1416,112 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 22172-2022 artfynd.xlsx", "A 22172-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 22172-2022 karta.png", "A 22172-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 22172-2022 georefererad karta.tif", "A 22172-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 22172-2022 FSC-klagomål.docx", "A 22172-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 22172-2022 FSC-klagomål mail.docx", "A 22172-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 22172-2022 tillsynsbegäran.docx", "A 22172-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 22172-2022 tillsynsbegäran mail.docx", "A 22172-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 39926-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>46290</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I9" t="n">
         <v>9.5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T9" t="n">
         <v>10</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Nästlav
@@ -1647,32 +1531,144 @@
 Äkta lopplummer</t>
         </is>
       </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 39926-2026 artfynd.xlsx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 39926-2026 karta.png", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 39926-2026 georefererad karta.tif", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 39926-2026 FSC-klagomål.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 39926-2026 FSC-klagomål mail.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 39926-2026 tillsynsbegäran.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 39926-2026 tillsynsbegäran mail.docx", "A 39926-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 39926-2026 artfynd.xlsx", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 39926-2026 karta.png", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 39926-2026 georefererad karta.tif", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 39926-2026 FSC-klagomål.docx", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 39926-2026 FSC-klagomål mail.docx", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 39926-2026 tillsynsbegäran.docx", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 39926-2026 tillsynsbegäran mail.docx", "A 39926-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
@@ -1696,7 +1692,7 @@
         <v>44952</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1792,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 37244-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1810,10 +1806,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44775</v>
+        <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,19 +1822,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1853,7 +1849,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1862,121 +1858,9 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 37244-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Talltita
@@ -1984,43 +1868,154 @@
 Grovticka</t>
         </is>
       </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Ladusvala
+Törnskata</t>
+        </is>
+      </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62578-2025</t>
+          <t>A 12620-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2034,10 +2029,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46007</v>
+        <v>44638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,19 +2045,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2074,171 +2069,167 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62578-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Mindre märgborre
 Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 27948-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Ladusvala
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12620-2022</t>
+          <t>A 54703-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2248,14 +2239,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44638</v>
+        <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,19 +2259,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2295,50 +2286,54 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
@@ -2362,7 +2357,7 @@
         <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2451,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 67244-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2470,10 +2465,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45618</v>
+        <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2485,89 +2480,89 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
+          <t>Igelkott
+Backdvärgmal</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67244-2021 artfynd.xlsx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67244-2021 karta.png", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67244-2021 georefererad karta.tif", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67244-2021 FSC-klagomål.docx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67244-2021 FSC-klagomål mail.docx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67244-2021 tillsynsbegäran.docx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67244-2021 tillsynsbegäran mail.docx", "A 67244-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 67244-2021</t>
+          <t>A 61275-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2577,14 +2572,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44523</v>
+        <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2596,16 +2591,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2614,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2626,59 +2616,59 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Backdvärgmal</t>
+          <t>Fläcknycklar
+Nattviol</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67244-2021 artfynd.xlsx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61275-2021 artfynd.xlsx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67244-2021 karta.png", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61275-2021 karta.png", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67244-2021 georefererad karta.tif", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61275-2021 georefererad karta.tif", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67244-2021 FSC-klagomål.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61275-2021 FSC-klagomål.docx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67244-2021 FSC-klagomål mail.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61275-2021 FSC-klagomål mail.docx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67244-2021 tillsynsbegäran.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61275-2021 tillsynsbegäran.docx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67244-2021 tillsynsbegäran mail.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61275-2021 tillsynsbegäran mail.docx", "A 61275-2021")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 61275-2021</t>
+          <t>A 43308-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2692,10 +2682,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44498</v>
+        <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2707,18 +2697,23 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2732,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2741,50 +2736,50 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar
-Nattviol</t>
+          <t>Dropptaggsvamp
+Tallticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61275-2021 artfynd.xlsx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61275-2021 karta.png", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61275-2021 georefererad karta.tif", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61275-2021 FSC-klagomål.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61275-2021 FSC-klagomål mail.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61275-2021 tillsynsbegäran.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61275-2021 tillsynsbegäran mail.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43308-2024</t>
+          <t>A 31575-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2798,10 +2793,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45568</v>
+        <v>44775</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,25 +2808,20 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2843,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2855,40 +2845,40 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
+          <t>Aspgelélav
+Dvärgtufs</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
     </row>
@@ -2912,7 +2902,7 @@
         <v>45499</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3006,7 +2996,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3020,10 +3010,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44775</v>
+        <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,13 +3026,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3066,53 +3056,52 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3126,10 +3115,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44915</v>
+        <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,10 +3131,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3154,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3166,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3178,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
@@ -3234,7 +3223,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3322,7 +3311,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3336,10 +3325,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,17 +3341,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3376,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3392,42 +3381,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3441,10 +3430,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46008</v>
+        <v>44523</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,11 +3445,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3493,63 +3487,67 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>S 5861-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44523</v>
+        <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,28 +3559,23 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3594,59 +3587,55 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 5861-2022 artfynd.xlsx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 5861-2022 karta.png", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 5861-2022 georefererad karta.tif", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 5861-2022 FSC-klagomål.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 5861-2022 FSC-klagomål mail.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 5861-2022 tillsynsbegäran.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 5861-2022 tillsynsbegäran mail.docx", "S 5861-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S 5861-2022</t>
+          <t>S 15-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3660,10 +3649,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44852</v>
+        <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3675,8 +3664,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3688,10 +3682,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3709,66 +3703,66 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 5861-2022 artfynd.xlsx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 15-2025 artfynd.xlsx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 5861-2022 karta.png", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 15-2025 karta.png", "S 15-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 5861-2022 georefererad karta.tif", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 15-2025 georefererad karta.tif", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 5861-2022 FSC-klagomål.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 15-2025 FSC-klagomål.docx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 5861-2022 FSC-klagomål mail.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 15-2025 FSC-klagomål mail.docx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 5861-2022 tillsynsbegäran.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 15-2025 tillsynsbegäran.docx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 5861-2022 tillsynsbegäran mail.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 15-2025 tillsynsbegäran mail.docx", "S 15-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 15-2025</t>
+          <t>A 2148-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45660</v>
+        <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3786,7 +3780,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3798,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3810,58 +3804,26 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Ädellav</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 15-2025 artfynd.xlsx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 15-2025 karta.png", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 15-2025 georefererad karta.tif", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 15-2025 FSC-klagomål.docx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 15-2025 FSC-klagomål mail.docx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 15-2025 tillsynsbegäran.docx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 15-2025 tillsynsbegäran mail.docx", "S 15-2025")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2148-2022</t>
+          <t>A 1910-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3878,7 +3840,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3896,7 +3858,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3939,7 +3901,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1910-2022</t>
+          <t>A 72508-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3953,10 +3915,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44575</v>
+        <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3974,7 +3936,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4017,7 +3979,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 72508-2021</t>
+          <t>A 15131-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4031,10 +3993,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44544</v>
+        <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4046,13 +4008,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4095,7 +4052,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15131-2022</t>
+          <t>A 19934-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,10 +4066,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44658</v>
+        <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,7 +4082,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4168,7 +4125,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19934-2022</t>
+          <t>A 19944-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4185,7 +4142,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4198,7 +4155,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4241,7 +4198,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19944-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4255,10 +4212,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44697</v>
+        <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4270,8 +4227,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4314,7 +4276,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4331,7 +4293,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4349,7 +4311,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4392,7 +4354,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 17173-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4406,10 +4368,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44569</v>
+        <v>44677</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4421,13 +4383,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4487,7 +4444,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4543,7 +4500,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17173-2022</t>
+          <t>A 10082-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4557,10 +4514,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44677</v>
+        <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4573,7 +4530,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4616,7 +4573,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10082-2022</t>
+          <t>A 28964-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4630,10 +4587,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44621</v>
+        <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4646,7 +4603,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4689,7 +4646,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28964-2022</t>
+          <t>A 18091-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4703,10 +4660,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44749</v>
+        <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4719,7 +4676,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4762,7 +4719,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18091-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4776,10 +4733,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44684</v>
+        <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4792,7 +4749,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4835,7 +4792,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4849,10 +4806,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44747</v>
+        <v>44851</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4865,7 +4822,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4908,7 +4865,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4922,10 +4879,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44915</v>
+        <v>45476</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4937,8 +4894,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4981,7 +4943,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4995,10 +4957,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>45476</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5010,8 +4972,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5054,7 +5021,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5068,10 +5035,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44937</v>
+        <v>45811</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5084,7 +5051,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5127,7 +5094,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5141,10 +5108,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45155</v>
+        <v>45447</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5156,8 +5123,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5200,7 +5172,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5214,10 +5186,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44951</v>
+        <v>44673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5229,13 +5201,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5278,7 +5245,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5288,14 +5255,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45518</v>
+        <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5308,7 +5275,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5351,7 +5318,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5365,10 +5332,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46049</v>
+        <v>45842</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5380,8 +5347,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5424,7 +5396,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5438,10 +5410,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45756</v>
+        <v>44917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5453,13 +5425,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5502,7 +5469,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5516,10 +5483,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44915</v>
+        <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5531,8 +5498,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5575,7 +5547,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5585,14 +5557,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45953</v>
+        <v>45861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5604,8 +5576,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5648,7 +5625,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5662,10 +5639,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45811</v>
+        <v>44952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5677,8 +5654,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5721,7 +5703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5731,14 +5713,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46087</v>
+        <v>45953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5750,13 +5732,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5799,7 +5776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5813,10 +5790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44673</v>
+        <v>46087</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5828,8 +5805,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5872,7 +5854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5886,10 +5868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44935</v>
+        <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5901,8 +5883,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5945,7 +5932,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5959,10 +5946,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44917</v>
+        <v>44565</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5974,8 +5961,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6018,7 +6010,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6032,10 +6024,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>45783</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6047,13 +6039,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6096,7 +6083,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6106,14 +6093,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45476</v>
+        <v>45518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6125,13 +6112,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6174,7 +6156,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6188,10 +6170,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45397</v>
+        <v>45387</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6204,7 +6186,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6247,7 +6229,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6261,10 +6243,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45842</v>
+        <v>44915</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6276,13 +6258,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6325,7 +6302,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6339,10 +6316,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45848</v>
+        <v>45995</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6355,7 +6332,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6398,7 +6375,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6412,10 +6389,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45995</v>
+        <v>45043</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6428,7 +6405,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6471,7 +6448,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6485,10 +6462,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45783</v>
+        <v>44920</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6501,7 +6478,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6544,7 +6521,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6558,10 +6535,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45166</v>
+        <v>45848</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6574,7 +6551,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6617,7 +6594,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6631,10 +6608,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45043</v>
+        <v>44966</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6647,7 +6624,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6690,7 +6667,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6704,10 +6681,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44673</v>
+        <v>45450</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6719,8 +6696,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6763,7 +6745,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6777,10 +6759,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45861</v>
+        <v>44678</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6792,13 +6774,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6841,7 +6818,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6855,10 +6832,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44565</v>
+        <v>45113</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6870,13 +6847,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6919,7 +6891,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6933,10 +6905,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45450</v>
+        <v>45842</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6997,7 +6969,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7011,10 +6983,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44678</v>
+        <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +6999,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7070,7 +7042,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7084,10 +7056,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45842</v>
+        <v>45629</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7099,13 +7071,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7148,7 +7115,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7158,14 +7125,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44966</v>
+        <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7178,7 +7145,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7221,7 +7188,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7231,14 +7198,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46161</v>
+        <v>44583</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7250,8 +7217,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7311,7 +7283,7 @@
         <v>45716</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7384,7 +7356,7 @@
         <v>45628</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7440,7 +7412,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7454,10 +7426,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46182</v>
+        <v>44673</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7470,7 +7442,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7513,7 +7485,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7523,14 +7495,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45300</v>
+        <v>46182</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7543,7 +7515,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10.1</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7586,7 +7558,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7600,10 +7572,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46203</v>
+        <v>44905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7615,8 +7587,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>13.8</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7659,7 +7636,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7673,10 +7650,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45113</v>
+        <v>45719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7689,7 +7666,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7732,7 +7709,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7746,10 +7723,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46210</v>
+        <v>44673</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7762,7 +7739,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7805,7 +7782,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7819,10 +7796,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46216</v>
+        <v>45397</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7835,7 +7812,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7878,7 +7855,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7892,10 +7869,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46216</v>
+        <v>46203</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7885,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>13.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7951,7 +7928,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7965,10 +7942,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46216</v>
+        <v>46210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7958,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8024,7 +8001,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8041,7 +8018,7 @@
         <v>46216</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8031,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8097,7 +8074,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8111,10 +8088,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45719</v>
+        <v>44915</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8104,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8170,7 +8147,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8184,10 +8161,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45082</v>
+        <v>46216</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8177,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8243,7 +8220,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8257,10 +8234,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45476</v>
+        <v>46216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8272,13 +8249,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8321,7 +8293,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8335,10 +8307,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45629</v>
+        <v>46216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8394,7 +8366,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8408,10 +8380,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45692</v>
+        <v>44951</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8423,8 +8395,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>11.2</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8467,7 +8444,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8484,7 +8461,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8502,7 +8479,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8545,7 +8522,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8555,14 +8532,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44924</v>
+        <v>45082</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8574,13 +8551,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8623,7 +8595,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8637,10 +8609,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44583</v>
+        <v>44677</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8652,13 +8624,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8701,7 +8668,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8715,10 +8682,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45387</v>
+        <v>44937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8731,7 +8698,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>13.7</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8774,7 +8741,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40142-2026</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8788,10 +8755,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46293</v>
+        <v>44937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8804,7 +8771,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8847,7 +8814,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8861,10 +8828,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45629</v>
+        <v>45692</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8877,7 +8844,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>11.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8920,7 +8887,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8930,14 +8897,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44905</v>
+        <v>44935</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8949,13 +8916,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8998,7 +8960,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9012,10 +8974,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44851</v>
+        <v>45166</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9028,7 +8990,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9071,7 +9033,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9081,14 +9043,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44673</v>
+        <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9101,7 +9063,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9144,7 +9106,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9158,10 +9120,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44677</v>
+        <v>45155</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9174,7 +9136,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9217,7 +9179,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 40142-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9231,10 +9193,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44952</v>
+        <v>46293</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9246,13 +9208,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9295,24 +9252,24 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>S 104-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44920</v>
+        <v>45302</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9368,7 +9325,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S 104-2024</t>
+          <t>S 156-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9382,10 +9339,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45302</v>
+        <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9398,7 +9355,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9438,10 +9395,10 @@
       </c>
       <c r="V105" s="2" t="inlineStr"/>
     </row>
-    <row r="106" ht="15" customHeight="1">
+    <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S 156-2024</t>
+          <t>S 2021-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9455,10 +9412,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45309</v>
+        <v>46210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9471,7 +9428,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9510,79 +9467,6 @@
         <v>0</v>
       </c>
       <c r="V106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>S 2021-2026</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3919-2023</t>
+          <t>A 31459-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44952</v>
+        <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -754,25 +754,20 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -787,18 +782,145 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
       </c>
       <c r="T3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Sårläka
+Tallticka
+Talltita
+Ullticka
+Älg
+Björksplintborre
+Mörk husmossa
+Thomsons trägnagare
+Tibast
+Blåsippa
+Spillkråka
+Sångsvan
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 3919-2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
         <v>62</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>61</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Stare
@@ -816,158 +938,36 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 31459-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U4" t="n">
-        <v>9</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Sårläka
-Tallticka
-Talltita
-Ullticka
-Älg
-Björksplintborre
-Mörk husmossa
-Thomsons trägnagare
-Tibast
-Blåsippa
-Spillkråka
-Sångsvan
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,11 +1592,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1605,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1617,21 +1622,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1639,153 +1756,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
         <v>45540</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12620-2022</t>
+          <t>A 62578-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44638</v>
+        <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,19 +2045,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2069,167 +2069,167 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 12620-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Taggfingersvamp
 Fällmossa
 Blåsippa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54703-2024</t>
+          <t>A 61363-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2239,14 +2239,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45618</v>
+        <v>44915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,17 +2259,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2292,159 +2292,159 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 54703-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 61363-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
         <v/>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31575-2022</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44775</v>
+        <v>45499</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2808,8 +2808,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2818,10 +2823,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2836,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2845,151 +2850,146 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31575-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Dvärgtufs</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 30949-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44523</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 838-2022</t>
+          <t>A 865-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4215,7 +4215,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 865-2022</t>
+          <t>A 838-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4293,7 +4293,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17173-2022</t>
+          <t>A 28405-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44677</v>
+        <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28405-2022</t>
+          <t>A 17173-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44747</v>
+        <v>44677</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44749</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44851</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4894,13 +4894,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4943,7 +4938,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4957,10 +4952,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45476</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4972,13 +4967,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5021,7 +5011,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5035,10 +5025,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45811</v>
+        <v>45155</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5051,7 +5041,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5094,7 +5084,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5108,10 +5098,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45447</v>
+        <v>44951</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,11 +5115,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5172,7 +5162,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5182,14 +5172,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44673</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5202,7 +5192,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5262,7 +5252,7 @@
         <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5318,7 +5308,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5332,10 +5322,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45842</v>
+        <v>45811</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5347,13 +5337,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5396,7 +5381,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5410,10 +5395,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44917</v>
+        <v>45756</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5425,8 +5410,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5469,7 +5459,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5483,10 +5473,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45756</v>
+        <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5498,13 +5488,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5547,7 +5532,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5561,10 +5546,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45861</v>
+        <v>44673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5576,13 +5561,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5625,7 +5605,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5639,10 +5619,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44952</v>
+        <v>46087</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5656,11 +5636,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5703,7 +5683,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5717,10 +5697,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45953</v>
+        <v>44935</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5733,7 +5713,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5776,7 +5756,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5790,10 +5770,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46087</v>
+        <v>44917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5805,13 +5785,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5854,7 +5829,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5864,14 +5839,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44924</v>
+        <v>45447</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5889,7 +5864,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5932,7 +5907,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5946,10 +5921,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44565</v>
+        <v>45842</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5967,7 +5942,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6010,7 +5985,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6020,14 +5995,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45783</v>
+        <v>45953</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6040,7 +6015,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6083,7 +6058,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6093,14 +6068,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45518</v>
+        <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6112,8 +6087,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6156,7 +6136,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6170,10 +6150,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45387</v>
+        <v>45861</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6185,8 +6165,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>13.7</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6229,7 +6214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6243,10 +6228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44915</v>
+        <v>45397</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6259,7 +6244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>13.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6302,7 +6287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60482-2025</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6316,10 +6301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45995</v>
+        <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6332,7 +6317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6375,7 +6360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 60482-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6389,10 +6374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45043</v>
+        <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6405,7 +6390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6448,7 +6433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6462,10 +6447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44920</v>
+        <v>45783</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6478,7 +6463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6521,7 +6506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6535,10 +6520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45848</v>
+        <v>45043</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6551,7 +6536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6594,7 +6579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6608,10 +6593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44966</v>
+        <v>45450</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6623,8 +6608,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6667,7 +6657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6681,10 +6671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45450</v>
+        <v>44678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6696,13 +6686,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6745,7 +6730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6759,10 +6744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44678</v>
+        <v>45842</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6774,8 +6759,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6818,7 +6808,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6828,14 +6818,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45113</v>
+        <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6848,7 +6838,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6891,7 +6881,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6905,10 +6895,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45842</v>
+        <v>45716</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6920,13 +6910,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6969,7 +6954,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6979,14 +6964,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45629</v>
+        <v>46182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6999,7 +6984,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7042,7 +7027,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7056,10 +7041,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45629</v>
+        <v>45166</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7072,7 +7057,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7115,7 +7100,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7125,14 +7110,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46161</v>
+        <v>44673</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7145,7 +7130,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7188,7 +7173,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7202,10 +7187,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44583</v>
+        <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7223,7 +7208,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7266,7 +7251,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7280,10 +7265,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45716</v>
+        <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7296,7 +7281,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7339,7 +7324,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7349,14 +7334,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45628</v>
+        <v>46210</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7369,7 +7354,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7412,7 +7397,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7422,14 +7407,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44673</v>
+        <v>46216</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7442,7 +7427,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7485,7 +7470,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7495,14 +7480,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46182</v>
+        <v>44966</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7515,7 +7500,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7558,7 +7543,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7572,10 +7557,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44905</v>
+        <v>46216</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7587,13 +7572,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7636,7 +7616,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7650,10 +7630,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45719</v>
+        <v>46216</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7666,7 +7646,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7709,7 +7689,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7723,10 +7703,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44673</v>
+        <v>46216</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7739,7 +7719,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7782,7 +7762,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7792,14 +7772,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45397</v>
+        <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,7 +7792,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>13.6</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7855,7 +7835,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7869,10 +7849,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46203</v>
+        <v>45300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,7 +7865,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.8</v>
+        <v>10.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7928,7 +7908,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7942,10 +7922,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46210</v>
+        <v>45113</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7958,7 +7938,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8001,7 +7981,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8015,10 +7995,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46216</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8031,7 +8011,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8074,7 +8054,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 24499-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8088,10 +8068,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44915</v>
+        <v>45082</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8104,7 +8084,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8147,7 +8127,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 40142-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8161,10 +8141,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46216</v>
+        <v>46293</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8177,7 +8157,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8220,7 +8200,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8234,10 +8214,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46216</v>
+        <v>45476</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8249,8 +8229,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8293,7 +8278,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8307,10 +8292,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46216</v>
+        <v>45629</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8366,7 +8351,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8380,10 +8365,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44951</v>
+        <v>45692</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8395,13 +8380,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>11.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8444,7 +8424,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8461,7 +8441,7 @@
         <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8479,7 +8459,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8522,7 +8502,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24499-2023</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8532,14 +8512,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45082</v>
+        <v>44924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8551,8 +8531,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8595,7 +8580,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8609,10 +8594,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44677</v>
+        <v>44583</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8624,8 +8609,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8668,7 +8658,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8682,10 +8672,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44937</v>
+        <v>45387</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8698,7 +8688,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>13.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8741,7 +8731,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8755,10 +8745,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44937</v>
+        <v>45629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8771,7 +8761,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8814,7 +8804,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8828,10 +8818,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45692</v>
+        <v>44905</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8843,8 +8833,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>11.2</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8887,7 +8882,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8897,14 +8892,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44935</v>
+        <v>44851</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8917,7 +8912,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8960,7 +8955,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8970,14 +8965,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45166</v>
+        <v>44673</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8990,7 +8985,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9033,7 +9028,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9047,10 +9042,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45300</v>
+        <v>44677</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9063,7 +9058,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10.1</v>
+        <v>5.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9106,7 +9101,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9120,10 +9115,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45155</v>
+        <v>44952</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9135,8 +9130,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9179,7 +9179,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40142-2026</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46293</v>
+        <v>44920</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>45302</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>46210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31459-2025</t>
+          <t>A 3919-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45833</v>
+        <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -754,20 +754,25 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -782,18 +787,140 @@
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
       </c>
       <c r="T3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U3" t="n">
+        <v>61</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Stare
+Brunlångöra
+Grönsångare
+Nordfladdermus
+Tallticka
+Tofsmes
+Dvärgpipistrell
+Grönsiska
+Kråka
+Kungsfågel
+Större brunfladdermus
+Svartvit flugsnappare
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 31459-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
         <v>17</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>9</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Sårläka
@@ -811,163 +938,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31459-2025 artfynd.xlsx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31459-2025 karta.png", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31459-2025 georefererad karta.tif", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31459-2025 FSC-klagomål.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31459-2025 FSC-klagomål mail.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31459-2025 tillsynsbegäran.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31459-2025 tillsynsbegäran mail.docx", "A 31459-2025")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31459-2025 prioriterade fågelarter.docx", "A 31459-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 3919-2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>62</v>
-      </c>
-      <c r="U4" t="n">
-        <v>61</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Stare
-Brunlångöra
-Grönsångare
-Nordfladdermus
-Tallticka
-Tofsmes
-Dvärgpipistrell
-Grönsiska
-Kråka
-Kungsfågel
-Större brunfladdermus
-Svartvit flugsnappare
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3919-2023 artfynd.xlsx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3919-2023 karta.png", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3919-2023 georefererad karta.tif", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3919-2023 FSC-klagomål.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3919-2023 FSC-klagomål mail.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3919-2023 tillsynsbegäran.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3919-2023 tillsynsbegäran mail.docx", "A 3919-2023")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3919-2023 prioriterade fågelarter.docx", "A 3919-2023")</f>
         <v/>
       </c>
     </row>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 3914-2023</t>
+          <t>A 31523-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44952</v>
+        <v>44775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,16 +1592,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1610,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1622,21 +1617,250 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Garnlav
+Tallticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 37244-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45540</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Talltita
+Vedskivlav
+Grovticka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 3914-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Gröngöling
@@ -1644,267 +1868,43 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31523-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Garnlav
-Tallticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 37244-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Talltita
-Vedskivlav
-Grovticka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 12620-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45817</v>
+        <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1970,266 +1970,266 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp
+Fällmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 62578-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>46007</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>3.4</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Mindre märgborre
 Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 12620-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp
-Fällmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 12620-2022 artfynd.xlsx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 12620-2022 karta.png", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 12620-2022 georefererad karta.tif", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 12620-2022 FSC-klagomål.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 12620-2022 FSC-klagomål mail.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 12620-2022 tillsynsbegäran.docx", "A 12620-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 12620-2022 tillsynsbegäran mail.docx", "A 12620-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61363-2022</t>
+          <t>A 54703-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2239,14 +2239,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44915</v>
+        <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,17 +2259,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2292,159 +2292,159 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44498</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>45568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 31575-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45499</v>
+        <v>44775</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2808,13 +2808,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2823,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2841,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2850,146 +2845,151 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Aspgelélav
+Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 30949-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31575-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44775</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Aspgelélav
-Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31575-2022 artfynd.xlsx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31575-2022 karta.png", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31575-2022 georefererad karta.tif", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31575-2022 FSC-klagomål.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31575-2022 FSC-klagomål mail.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31575-2022 tillsynsbegäran.docx", "A 31575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31575-2022 tillsynsbegäran mail.docx", "A 31575-2022")</f>
         <v/>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
         <v>44915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3223,7 +3223,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3236,17 +3236,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3276,42 +3276,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3328,7 +3328,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,16 +3341,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3381,35 +3381,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         <v>44523</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45660</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44697</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44697</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44569</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>44747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17173-2022</t>
+          <t>A 18091-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44677</v>
+        <v>44684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10082-2022</t>
+          <t>A 17173-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44621</v>
+        <v>44677</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28964-2022</t>
+          <t>A 28399-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44749</v>
+        <v>44747</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18091-2022</t>
+          <t>A 10082-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44684</v>
+        <v>44621</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28399-2022</t>
+          <t>A 28964-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44747</v>
+        <v>44749</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61370-2022</t>
+          <t>A 470-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>44565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4821,8 +4821,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4865,7 +4870,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1603-2023</t>
+          <t>A 46688-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4879,10 +4884,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>44851</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4895,7 +4900,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4938,7 +4943,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1605-2023</t>
+          <t>A 33158-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4948,14 +4953,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>45518</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4968,7 +4973,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5011,7 +5016,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37037-2023</t>
+          <t>A 13366-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5025,10 +5030,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45155</v>
+        <v>45387</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5041,7 +5046,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>13.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5084,7 +5089,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3828-2023</t>
+          <t>A 61360-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5098,10 +5103,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44951</v>
+        <v>44915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5113,13 +5118,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33158-2024</t>
+          <t>A 27137-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45518</v>
+        <v>45811</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5235,7 +5235,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5038-2026</t>
+          <t>A 28143-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46049</v>
+        <v>45476</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5264,8 +5264,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5308,7 +5313,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27137-2025</t>
+          <t>A 62108-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5322,10 +5327,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45811</v>
+        <v>44920</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5338,7 +5343,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5381,7 +5386,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17353-2025</t>
+          <t>A 6655-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5395,10 +5400,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45756</v>
+        <v>44966</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5410,13 +5415,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5459,7 +5459,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61360-2022</t>
+          <t>A 28146-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44915</v>
+        <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5488,8 +5488,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5532,7 +5537,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16728-2022</t>
+          <t>A 34034-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5546,10 +5551,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44673</v>
+        <v>45842</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5561,8 +5566,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5605,7 +5615,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12345-2026</t>
+          <t>A 31134-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5619,10 +5629,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46087</v>
+        <v>45113</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5634,13 +5644,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5683,7 +5688,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1136-2023</t>
+          <t>A 22528-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5693,14 +5698,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44935</v>
+        <v>45447</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5712,8 +5717,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5756,7 +5766,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61710-2022</t>
+          <t>A 16803-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5770,10 +5780,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44917</v>
+        <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5786,7 +5796,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5829,7 +5839,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22528-2024</t>
+          <t>A 52220-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5839,14 +5849,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45447</v>
+        <v>45953</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5858,13 +5868,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5907,7 +5912,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34034-2025</t>
+          <t>A 57048-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5921,10 +5926,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45842</v>
+        <v>45629</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5936,13 +5941,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5985,7 +5985,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52220-2025</t>
+          <t>A 57055-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5995,14 +5995,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45953</v>
+        <v>45629</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28143-2024</t>
+          <t>A 35819-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45476</v>
+        <v>45861</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6136,7 +6136,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35819-2025</t>
+          <t>A 61710-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45861</v>
+        <v>44917</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6165,13 +6165,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6214,7 +6209,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14776-2024</t>
+          <t>A 3326-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6228,10 +6223,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45397</v>
+        <v>44583</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6243,8 +6238,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>13.6</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6287,7 +6287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34713-2025</t>
+          <t>A 17353-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45848</v>
+        <v>45756</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6316,8 +6316,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
         <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6433,7 +6438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21796-2025</t>
+          <t>A 18711-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6447,10 +6452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45783</v>
+        <v>45043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6463,7 +6468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6506,7 +6511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18711-2023</t>
+          <t>A 56909-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6516,14 +6521,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45043</v>
+        <v>45628</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6536,7 +6541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6579,7 +6584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23144-2024</t>
+          <t>A 34713-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6593,10 +6598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45450</v>
+        <v>45848</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6608,13 +6613,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6657,7 +6657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17263-2022</t>
+          <t>A 23144-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44678</v>
+        <v>45450</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6686,8 +6686,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6730,7 +6735,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34038-2025</t>
+          <t>A 3917-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6744,10 +6749,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45842</v>
+        <v>44952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6761,11 +6766,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6808,7 +6813,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23198-2026</t>
+          <t>A 17263-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6818,14 +6823,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46161</v>
+        <v>44678</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6838,7 +6843,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6881,7 +6886,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9865-2025</t>
+          <t>A 16738-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6891,14 +6896,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45716</v>
+        <v>44673</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6911,7 +6916,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6954,7 +6959,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26249-2026</t>
+          <t>A 34038-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6964,14 +6969,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46182</v>
+        <v>45842</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6983,8 +6988,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7027,7 +7037,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39394-2023</t>
+          <t>A 59379-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7041,10 +7051,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45166</v>
+        <v>44905</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7056,8 +7066,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7100,7 +7115,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16803-2022</t>
+          <t>A 23198-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7110,14 +7125,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44673</v>
+        <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7130,7 +7145,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7173,7 +7188,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 470-2022</t>
+          <t>A 10185-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7187,10 +7202,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44565</v>
+        <v>45719</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7202,13 +7217,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7251,7 +7261,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29443-2026</t>
+          <t>A 9865-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7265,10 +7275,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46203</v>
+        <v>45716</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7281,7 +7291,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.8</v>
+        <v>7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7324,7 +7334,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30599-2026</t>
+          <t>A 16728-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7338,10 +7348,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46210</v>
+        <v>44673</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7354,7 +7364,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7397,7 +7407,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31154-2026</t>
+          <t>A 544-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7407,14 +7417,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46216</v>
+        <v>44924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7426,8 +7436,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7470,7 +7485,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6655-2023</t>
+          <t>A 14776-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7484,10 +7499,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44966</v>
+        <v>45397</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7500,7 +7515,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>13.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7543,7 +7558,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31146-2026</t>
+          <t>A 26249-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7553,14 +7568,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46216</v>
+        <v>46182</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7573,7 +7588,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7616,7 +7631,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31149-2026</t>
+          <t>A 5038-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7630,10 +7645,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46216</v>
+        <v>46049</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7646,7 +7661,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7689,7 +7704,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31156-2026</t>
+          <t>A 61370-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7703,10 +7718,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46216</v>
+        <v>44915</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7719,7 +7734,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7762,7 +7777,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56909-2024</t>
+          <t>A 3817-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7772,14 +7787,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45628</v>
+        <v>44951</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7791,8 +7806,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7835,7 +7855,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 845-2024</t>
+          <t>A 3828-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7849,10 +7869,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45300</v>
+        <v>44951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7864,8 +7884,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>10.1</v>
+        <v>3.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7908,7 +7933,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31134-2023</t>
+          <t>A 12345-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7922,10 +7947,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45113</v>
+        <v>46087</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7937,8 +7962,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7981,7 +8011,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10185-2025</t>
+          <t>A 29443-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7995,10 +8025,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45719</v>
+        <v>46203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8011,7 +8041,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>13.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8071,7 +8101,7 @@
         <v>45082</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8157,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40142-2026</t>
+          <t>A 17196-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8141,10 +8171,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46293</v>
+        <v>44677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8157,7 +8187,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8200,7 +8230,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28146-2024</t>
+          <t>A 30599-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8214,10 +8244,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45476</v>
+        <v>46210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8229,13 +8259,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8278,7 +8303,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 57048-2024</t>
+          <t>A 31149-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8292,10 +8317,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45629</v>
+        <v>46216</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8308,7 +8333,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8351,7 +8376,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5286-2025</t>
+          <t>A 31156-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8365,10 +8390,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45692</v>
+        <v>46216</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8381,7 +8406,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>11.2</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8424,7 +8449,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3817-2023</t>
+          <t>A 31146-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8438,10 +8463,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44951</v>
+        <v>46216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8453,13 +8478,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8502,7 +8522,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 544-2023</t>
+          <t>A 1603-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8512,14 +8532,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44924</v>
+        <v>44937</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8531,13 +8551,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8580,7 +8595,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3326-2022</t>
+          <t>A 1605-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8594,10 +8609,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44583</v>
+        <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8609,13 +8624,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8658,7 +8668,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13366-2024</t>
+          <t>A 31154-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8672,10 +8682,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45387</v>
+        <v>46216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8688,7 +8698,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>13.7</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8731,7 +8741,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57055-2024</t>
+          <t>A 21796-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8745,10 +8755,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45629</v>
+        <v>45783</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8761,7 +8771,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8804,7 +8814,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59379-2022</t>
+          <t>A 5286-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8818,10 +8828,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44905</v>
+        <v>45692</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8833,13 +8843,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>11.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8882,7 +8887,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46688-2022</t>
+          <t>A 1136-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8892,14 +8897,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44851</v>
+        <v>44935</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8912,7 +8917,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8955,7 +8960,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16738-2022</t>
+          <t>A 39394-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8965,14 +8970,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44673</v>
+        <v>45166</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8985,7 +8990,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9028,7 +9033,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17196-2022</t>
+          <t>A 845-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9042,10 +9047,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44677</v>
+        <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9058,7 +9063,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9101,7 +9106,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 3917-2023</t>
+          <t>A 37037-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9115,10 +9120,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44952</v>
+        <v>45155</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9130,13 +9135,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9179,7 +9179,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62108-2022</t>
+          <t>A 40142-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44920</v>
+        <v>46293</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>45302</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>46210</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt ÖSTERÅKER.xlsx
+++ b/Översikt ÖSTERÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE106"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45583</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45833</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>46178</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45499</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31523-2022</t>
+          <t>A 3914-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44775</v>
+        <v>44952</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,11 +1592,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1605,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1617,21 +1622,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Gröngöling
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31523-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44775</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -1639,111 +1756,111 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31523-2022 artfynd.xlsx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31523-2022 karta.png", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31523-2022 georefererad karta.tif", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31523-2022 FSC-klagomål.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31523-2022 FSC-klagomål mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31523-2022 tillsynsbegäran.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31523-2022 tillsynsbegäran mail.docx", "A 31523-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 31523-2022 prioriterade fågelarter.docx", "A 31523-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 37244-2024</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45540</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Talltita
@@ -1751,153 +1868,36 @@
 Grovticka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 37244-2024 artfynd.xlsx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 37244-2024 karta.png", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 37244-2024 georefererad karta.tif", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 37244-2024 FSC-klagomål.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 37244-2024 FSC-klagomål mail.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 37244-2024 tillsynsbegäran.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 37244-2024 tillsynsbegäran mail.docx", "A 37244-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 37244-2024 prioriterade fågelarter.docx", "A 37244-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 3914-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Gröngöling
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 3914-2023 artfynd.xlsx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 3914-2023 karta.png", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 3914-2023 georefererad karta.tif", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 3914-2023 FSC-klagomål.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 3914-2023 FSC-klagomål mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 3914-2023 tillsynsbegäran.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 3914-2023 tillsynsbegäran mail.docx", "A 3914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 3914-2023 prioriterade fågelarter.docx", "A 3914-2023")</f>
         <v/>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         <v>44638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 27948-2025</t>
+          <t>A 62578-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45817</v>
+        <v>46007</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2065,282 +2065,282 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Mindre märgborre
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 61363-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27948-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Ladusvala
 Törnskata</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 27948-2025 artfynd.xlsx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 27948-2025 karta.png", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 27948-2025 georefererad karta.tif", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 27948-2025 FSC-klagomål.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 27948-2025 FSC-klagomål mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 27948-2025 tillsynsbegäran.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 27948-2025 tillsynsbegäran mail.docx", "A 27948-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 27948-2025 prioriterade fågelarter.docx", "A 27948-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62578-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Mindre märgborre
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62578-2025 artfynd.xlsx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62578-2025 karta.png", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62578-2025 georefererad karta.tif", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62578-2025 FSC-klagomål.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62578-2025 FSC-klagomål mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62578-2025 tillsynsbegäran.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62578-2025 tillsynsbegäran mail.docx", "A 62578-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 54703-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45618</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖSTERÅKER</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 54703-2024 artfynd.xlsx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 54703-2024 karta.png", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 54703-2024 georefererad karta.tif", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 54703-2024 FSC-klagomål.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 54703-2024 FSC-klagomål mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 54703-2024 tillsynsbegäran.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 54703-2024 tillsynsbegäran mail.docx", "A 54703-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 54703-2024 prioriterade fågelarter.docx", "A 54703-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61363-2022</t>
+          <t>A 67244-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44915</v>
+        <v>44523</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,22 +2367,27 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>ÖSTERÅKER</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>5.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2397,61 +2402,56 @@
         <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp
-Skuggblåslav
-Tjäder</t>
+          <t>Igelkott
+Backdvärgmal</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61363-2022 artfynd.xlsx", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67244-2021 artfynd.xlsx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61363-2022 karta.png", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67244-2021 karta.png", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61363-2022 georefererad karta.tif", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67244-2021 georefererad karta.tif", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61363-2022 FSC-klagomål.docx", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67244-2021 FSC-klagomål.docx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61363-2022 FSC-klagomål mail.docx", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67244-2021 FSC-klagomål mail.docx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61363-2022 tillsynsbegäran.docx", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67244-2021 tillsynsbegäran.docx", "A 67244-2021")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61363-2022 tillsynsbegäran mail.docx", "A 61363-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 61363-2022 prioriterade fågelarter.docx", "A 61363-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67244-2021 tillsynsbegäran mail.docx", "A 67244-2021")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 67244-2021</t>
+          <t>A 61275-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2461,14 +2461,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44523</v>
+        <v>44498</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,16 +2480,11 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2498,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2510,59 +2505,59 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott
-Backdvärgmal</t>
+          <t>Fläcknycklar
+Nattviol</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67244-2021 artfynd.xlsx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61275-2021 artfynd.xlsx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67244-2021 karta.png", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61275-2021 karta.png", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67244-2021 georefererad karta.tif", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61275-2021 georefererad karta.tif", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67244-2021 FSC-klagomål.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61275-2021 FSC-klagomål.docx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67244-2021 FSC-klagomål mail.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61275-2021 FSC-klagomål mail.docx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67244-2021 tillsynsbegäran.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61275-2021 tillsynsbegäran.docx", "A 61275-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67244-2021 tillsynsbegäran mail.docx", "A 67244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61275-2021 tillsynsbegäran mail.docx", "A 61275-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 61275-2021</t>
+          <t>A 43308-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2576,10 +2571,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44498</v>
+        <v>45568</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2591,18 +2586,23 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2625,50 +2625,50 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar
-Nattviol</t>
+          <t>Dropptaggsvamp
+Tallticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61275-2021 artfynd.xlsx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61275-2021 karta.png", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61275-2021 georefererad karta.tif", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61275-2021 FSC-klagomål.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61275-2021 FSC-klagomål mail.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61275-2021 tillsynsbegäran.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61275-2021 tillsynsbegäran mail.docx", "A 61275-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43308-2024</t>
+          <t>A 30949-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45568</v>
+        <v>45499</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2709,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2743,36 +2743,36 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
+          <t>Tallticka
+Blåmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 43308-2024 artfynd.xlsx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 43308-2024 karta.png", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 43308-2024 georefererad karta.tif", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 43308-2024 FSC-klagomål.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 43308-2024 FSC-klagomål mail.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 43308-2024 tillsynsbegäran.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 43308-2024 tillsynsbegäran mail.docx", "A 43308-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
         <v/>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
         <v>44775</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30949-2024</t>
+          <t>A 61323-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45499</v>
+        <v>44915</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2914,25 +2914,20 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2947,56 +2942,55 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tallticka
-Blåmossa</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 30949-2024 artfynd.xlsx", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 30949-2024 karta.png", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 30949-2024 georefererad karta.tif", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 30949-2024 FSC-klagomål.docx", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 30949-2024 FSC-klagomål mail.docx", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 30949-2024 tillsynsbegäran.docx", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 30949-2024 tillsynsbegäran mail.docx", "A 30949-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61323-2022</t>
+          <t>A 62831-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3010,10 +3004,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44915</v>
+        <v>46008</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3026,19 +3020,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3050,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3062,46 +3056,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 61323-2022 artfynd.xlsx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 61323-2022 karta.png", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 61323-2022 georefererad karta.tif", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 61323-2022 FSC-klagomål.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 61323-2022 FSC-klagomål mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 61323-2022 tillsynsbegäran.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 61323-2022 tillsynsbegäran mail.docx", "A 61323-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31716-2025</t>
+          <t>A 62839-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3115,10 +3109,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>46008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3131,17 +3125,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3155,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3171,42 +3165,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62839-2025</t>
+          <t>A 67265-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3220,10 +3214,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46008</v>
+        <v>44523</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3235,11 +3229,16 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3272,46 +3271,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62839-2025 artfynd.xlsx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62839-2025 karta.png", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62839-2025 georefererad karta.tif", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62839-2025 FSC-klagomål.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62839-2025 FSC-klagomål mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62839-2025 tillsynsbegäran.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62839-2025 tillsynsbegäran mail.docx", "A 62839-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62831-2025</t>
+          <t>A 31716-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3325,10 +3328,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46008</v>
+        <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,13 +3344,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3381,59 +3384,59 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 62831-2025 artfynd.xlsx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 31716-2025 artfynd.xlsx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 62831-2025 karta.png", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 31716-2025 karta.png", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 62831-2025 georefererad karta.tif", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 31716-2025 georefererad karta.tif", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 62831-2025 FSC-klagomål.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 31716-2025 FSC-klagomål.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 62831-2025 FSC-klagomål mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 31716-2025 FSC-klagomål mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 62831-2025 tillsynsbegäran.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 31716-2025 tillsynsbegäran.docx", "A 31716-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 62831-2025 tillsynsbegäran mail.docx", "A 62831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 31716-2025 tillsynsbegäran mail.docx", "A 31716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 67265-2021</t>
+          <t>S 5861-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44523</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3445,28 +3448,23 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3478,59 +3476,55 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/A 67265-2021 artfynd.xlsx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 5861-2022 artfynd.xlsx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/A 67265-2021 karta.png", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 5861-2022 karta.png", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/A 67265-2021 georefererad karta.tif", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 5861-2022 georefererad karta.tif", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/A 67265-2021 FSC-klagomål.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 5861-2022 FSC-klagomål.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/A 67265-2021 FSC-klagomål mail.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 5861-2022 FSC-klagomål mail.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/A 67265-2021 tillsynsbegäran.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 5861-2022 tillsynsbegäran.docx", "S 5861-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/A 67265-2021 tillsynsbegäran mail.docx", "A 67265-2021")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/fåglar/A 67265-2021 prioriterade fågelarter.docx", "A 67265-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 5861-2022 tillsynsbegäran mail.docx", "S 5861-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S 5861-2022</t>
+          <t>S 15-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3544,10 +3538,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44852</v>
+        <v>45660</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3559,8 +3553,13 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3572,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3593,66 +3592,66 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 5861-2022 artfynd.xlsx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 15-2025 artfynd.xlsx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 5861-2022 karta.png", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 15-2025 karta.png", "S 15-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 5861-2022 georefererad karta.tif", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 15-2025 georefererad karta.tif", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 5861-2022 FSC-klagomål.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 15-2025 FSC-klagomål.docx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 5861-2022 FSC-klagomål mail.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 15-2025 FSC-klagomål mail.docx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 5861-2022 tillsynsbegäran.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 15-2025 tillsynsbegäran.docx", "S 15-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 5861-2022 tillsynsbegäran mail.docx", "S 5861-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 15-2025 tillsynsbegäran mail.docx", "S 15-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S 15-2025</t>
+          <t>A 2148-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45660</v>
+        <v>44575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3670,7 +3669,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3682,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3694,58 +3693,26 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Ädellav</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/artfynd/S 15-2025 artfynd.xlsx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor/S 15-2025 karta.png", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/kartor_geotiff/S 15-2025 georefererad karta.tif", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomål/S 15-2025 FSC-klagomål.docx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/klagomålsmail/S 15-2025 FSC-klagomål mail.docx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsyn/S 15-2025 tillsynsbegäran.docx", "S 15-2025")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0117/tillsynsmail/S 15-2025 tillsynsbegäran mail.docx", "S 15-2025")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2148-2022</t>
+          <t>A 1910-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3762,7 +3729,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3780,7 +3747,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3823,7 +3790,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1910-2022</t>
+          <t>A 72508-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3804,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44575</v>
+        <v>44544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3858,7 +3825,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3901,7 +3868,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 72508-2021</t>
+          <t>A 15131-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3915,10 +3882,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44544</v>
+        <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3930,13 +3897,8 @@
           <t>ÖSTERÅKER</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3979,7 +3941,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15131-2022</t>
+          <t>A 19934-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3993,10 +3955,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44658</v>
+        <v>44697</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4009,7 +3971,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4052,7 +4014,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <